--- a/NEB-ALCARRIA-PRESUPUESTO.xlsx
+++ b/NEB-ALCARRIA-PRESUPUESTO.xlsx
@@ -25,8 +25,10 @@
     <definedName function="false" hidden="false" name="actividades_dias" vbProcedure="false">ACTIVIDADES!$D$5:$D$50</definedName>
     <definedName function="false" hidden="false" name="actividades_ediciones" vbProcedure="false">ACTIVIDADES!$E$5:$E$50</definedName>
     <definedName function="false" hidden="false" name="alojamiento" vbProcedure="false">PARAMETROS!$C$21</definedName>
+    <definedName function="false" hidden="false" name="alojamiento_copr" vbProcedure="false">PARAMETROS!$C$57</definedName>
     <definedName function="false" hidden="false" name="bus_dia" vbProcedure="false">PARAMETROS!$C$52</definedName>
     <definedName function="false" hidden="false" name="cap_bus" vbProcedure="false">PARAMETROS!$C$53</definedName>
+    <definedName function="false" hidden="false" name="cap_vehiculo_copr" vbProcedure="false">PARAMETROS!$C$60</definedName>
     <definedName function="false" hidden="false" name="ext_h" vbProcedure="false">PARAMETROS!$C$14</definedName>
     <definedName function="false" hidden="false" name="gp1_ss" vbProcedure="false">PARAMETROS!$C$7</definedName>
     <definedName function="false" hidden="false" name="gp2_ss" vbProcedure="false">PARAMETROS!$C$8</definedName>
@@ -38,11 +40,14 @@
     <definedName function="false" hidden="false" name="km_coche" vbProcedure="false">PARAMETROS!$C$24</definedName>
     <definedName function="false" hidden="false" name="km_madrid_pastrana" vbProcedure="false">PARAMETROS!$C$51</definedName>
     <definedName function="false" hidden="false" name="manut_dia" vbProcedure="false">PARAMETROS!$C$22</definedName>
+    <definedName function="false" hidden="false" name="manut_dia_copr" vbProcedure="false">PARAMETROS!$C$58</definedName>
     <definedName function="false" hidden="false" name="manut_med" vbProcedure="false">PARAMETROS!$C$23</definedName>
+    <definedName function="false" hidden="false" name="manut_med_copr" vbProcedure="false">PARAMETROS!$C$59</definedName>
     <definedName function="false" hidden="false" name="meses_p1" vbProcedure="false">PARAMETROS!$C$46</definedName>
     <definedName function="false" hidden="false" name="meses_p2" vbProcedure="false">PARAMETROS!$C$47</definedName>
     <definedName function="false" hidden="false" name="meses_proy" vbProcedure="false">PARAMETROS!$C$48</definedName>
     <definedName function="false" hidden="false" name="min_subv" vbProcedure="false">PARAMETROS!$C$31</definedName>
+    <definedName function="false" hidden="false" name="n_vehiculos_copr" vbProcedure="false">PARAMETROS!$C$61</definedName>
     <definedName function="false" hidden="false" name="pct_p1" vbProcedure="false">PARAMETROS!$C$44</definedName>
     <definedName function="false" hidden="false" name="pct_p2" vbProcedure="false">PARAMETROS!$C$45</definedName>
     <definedName function="false" hidden="false" name="ratio_prep" vbProcedure="false">PARAMETROS!$C$16</definedName>
@@ -67,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="685">
   <si>
     <t xml:space="preserve">NEB-ALCARRIA — Presupuesto</t>
   </si>
@@ -552,15 +557,57 @@
     <t xml:space="preserve">€/día</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimación de mercado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capacidad bus</t>
+    <t xml:space="preserve">Estimación de mercado (residual si COPRODELI no cubre)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacidad bus alquilado externo</t>
   </si>
   <si>
     <t xml:space="preserve">plazas</t>
   </si>
   <si>
+    <t xml:space="preserve">E · PRECIOS COPRODELI (efectivos · todos por debajo de topes oficiales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alojamiento (residencia COPRODELI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€/noche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tope oficial 65,97 € → -17 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manutención día completo COPRODELI (almuerzo+cena)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 € almuerzo + 15 € cena. Tope oficial 37,40 € → -20 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Almuerzo o cena COPRODELI (media dieta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€/cubierto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tope oficial 18,70 € → -20 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacidad vehículo COPRODELI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furgoneta/vehículo medio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nº vehículos COPRODELI disponibles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vehículos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total 80 plazas (cubre todas las actividades). Agrupar asistentes en vehículos compartidos vs. desplazamiento individual</t>
+  </si>
+  <si>
     <t xml:space="preserve">REFERENCIAS NORMATIVAS — base documental de cada parámetro</t>
   </si>
   <si>
@@ -1812,31 +1859,40 @@
     <t xml:space="preserve">Cuota total</t>
   </si>
   <si>
-    <t xml:space="preserve">Dron multispectral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DJI Mavic 3M + cámara multiespectral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activo UPM (drones GeoSo2)</t>
+    <t xml:space="preserve">Dron 4K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuerpo del dron 4K (proveedor: importador de drones)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt; 5.000 €. Activo UPM (drones GeoSo2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cámara multispectral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cámara multispectral compatible (proveedor especializado en óptica multiespectral, distinto del importador del dron)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt; 5.000 €. Activo UPM. Justificación técnica: ningún proveedor de dron 4K ofrece la óptica multispectral con calidad equivalente</t>
   </si>
   <si>
     <t xml:space="preserve">Sensores IoT</t>
   </si>
   <si>
-    <t xml:space="preserve">Lote 20 sensores LoRa humedad/meteo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quedan en parcela; activos UPM</t>
+    <t xml:space="preserve">Lote de 15 sensores LoRa humedad/meteo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt; 5.000 €. Quedan en parcela; activos UPM</t>
   </si>
   <si>
     <t xml:space="preserve">Software de cálculo de estructuras</t>
   </si>
   <si>
-    <t xml:space="preserve">Licencia anual de software estructural (cálculo del domo geodésico)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licencia anual prorrateada al periodo</t>
+    <t xml:space="preserve">3 licencias anuales × 1.000 € c/u (IP estructural + 2 colaboradores GeoSo2/UPM trabajando en paralelo en el cálculo del domo geodésico)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 × licencia anual prorrateada al periodo</t>
   </si>
   <si>
     <t xml:space="preserve">Servidor/gateway IoT</t>
@@ -1860,43 +1916,61 @@
     <t xml:space="preserve">Cimentación domo</t>
   </si>
   <si>
-    <t xml:space="preserve">Zapatas, hormigón armado, replanteo del polígono geodésico</t>
+    <t xml:space="preserve">Zapatas, hormigón armado, replanteo del polígono geodésico (proveedor de obra civil local)</t>
   </si>
   <si>
     <t xml:space="preserve">A10–A11</t>
   </si>
   <si>
-    <t xml:space="preserve">Estructura del domo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Madera precortada + anclajes + herrajes metálicos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cubierta y suelos del domo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cubierta exterior + acabado interior del suelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aislamiento del domo (hidrófugo + térmico)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corcho aglomerado + impermeabilización exterior</t>
+    <t xml:space="preserve">Listones del domo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madera precortada para los listones del domo geodésico (proveedor: aserradero / carpintería)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tornillería y herramientas del domo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tornillería de precisión, herrajes metálicos y herramientas auxiliares (proveedor: ferretería industrial / ingeniería metálica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cubierta del domo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cubierta exterior del domo (proveedor especializado en cubiertas técnicas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aislamiento térmico del domo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material de aislamiento térmico — corcho aglomerado o equivalente (proveedor de materiales aislantes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aislamiento hidrófugo del domo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impermeabilización exterior — membrana hidrófuga o equivalente (proveedor de impermeabilización)</t>
   </si>
   <si>
     <t xml:space="preserve">Ventanas del domo</t>
   </si>
   <si>
-    <t xml:space="preserve">Ventanas + ventilación pasiva</t>
+    <t xml:space="preserve">Ventanas y elementos de ventilación pasiva (proveedor de carpintería de ventanas)</t>
   </si>
   <si>
     <t xml:space="preserve">A12–A13</t>
   </si>
   <si>
-    <t xml:space="preserve">Cableado y sistema solar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre-cableado eléctrico + paneles FV + inversor + baterías</t>
+    <t xml:space="preserve">Paneles fotovoltaicos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paneles FV bifaciales N-type 5 kW (proveedor: importador especializado en paneles solares)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baterías, cableado e instalación FV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baterías + cableado eléctrico + montaje (proveedor: instalador eléctrico local con certificación BT)</t>
   </si>
   <si>
     <t xml:space="preserve">Conectividad satelital</t>
@@ -1971,7 +2045,7 @@
     <t xml:space="preserve">A.5 Coordinación</t>
   </si>
   <si>
-    <t xml:space="preserve">B.1 Viajes y dietas</t>
+    <t xml:space="preserve">B.1 Viajes y dietas (precios COPRODELI · por debajo de topes oficiales)</t>
   </si>
   <si>
     <t xml:space="preserve">B.2 Entornos virtuales</t>
@@ -3028,7 +3102,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F53"/>
+  <dimension ref="B2:F61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -3770,14 +3844,126 @@
       </c>
       <c r="F53" s="15"/>
     </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="C57" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="D57" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="E57" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F57" s="15" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C58" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="D58" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F58" s="15" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C59" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D59" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="E59" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F59" s="15" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="C60" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="D60" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="E60" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F60" s="15" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="C61" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="E61" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>177</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B55:F55"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3808,7 +3994,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3819,7 +4005,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3839,13 +4025,13 @@
         <v>49</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>52</v>
@@ -3856,22 +4042,22 @@
         <v>55</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3879,22 +4065,22 @@
         <v>58</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3902,22 +4088,22 @@
         <v>60</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3925,22 +4111,22 @@
         <v>62</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3948,22 +4134,22 @@
         <v>64</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3974,19 +4160,19 @@
         <v>66</v>
       </c>
       <c r="C10" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="E10" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="D10" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>178</v>
-      </c>
       <c r="F10" s="23" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3997,16 +4183,16 @@
         <v>68</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="G11" s="20"/>
     </row>
@@ -4015,22 +4201,22 @@
         <v>71</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4038,22 +4224,22 @@
         <v>75</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4061,22 +4247,22 @@
         <v>79</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4087,19 +4273,19 @@
         <v>82</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4110,16 +4296,16 @@
         <v>86</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="G16" s="23"/>
     </row>
@@ -4128,22 +4314,22 @@
         <v>91</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4151,19 +4337,19 @@
         <v>95</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="G18" s="23"/>
     </row>
@@ -4172,19 +4358,19 @@
         <v>97</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="G19" s="20"/>
     </row>
@@ -4196,16 +4382,16 @@
         <v>99</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="G20" s="23"/>
     </row>
@@ -4214,22 +4400,22 @@
         <v>104</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4237,19 +4423,19 @@
         <v>107</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="G22" s="23"/>
     </row>
@@ -4258,22 +4444,22 @@
         <v>110</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4281,22 +4467,22 @@
         <v>113</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4304,22 +4490,22 @@
         <v>117</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4330,19 +4516,19 @@
         <v>119</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4353,13 +4539,13 @@
         <v>122</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="F27" s="20"/>
       <c r="G27" s="20"/>
@@ -4372,16 +4558,16 @@
         <v>124</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="G28" s="23"/>
     </row>
@@ -4393,13 +4579,13 @@
         <v>126</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
@@ -4409,22 +4595,22 @@
         <v>130</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="G30" s="23" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4432,19 +4618,19 @@
         <v>133</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="G31" s="20"/>
     </row>
@@ -4453,19 +4639,19 @@
         <v>136</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="G32" s="23"/>
     </row>
@@ -4474,19 +4660,19 @@
         <v>139</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -4495,152 +4681,152 @@
         <v>142</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="F34" s="23" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="G34" s="23" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="C35" s="20" t="s">
         <v>138</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="22" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="F36" s="23" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="G36" s="23"/>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="C37" s="20" t="s">
         <v>138</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="22" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="C38" s="23" t="s">
         <v>138</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="F38" s="23"/>
       <c r="G38" s="23"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="G39" s="20"/>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="22" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="C40" s="23" t="s">
         <v>138</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="F40" s="23" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="G40" s="23" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -4678,7 +4864,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -4692,7 +4878,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4706,45 +4892,45 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="D5" s="28" t="n">
         <v>1</v>
@@ -4763,21 +4949,21 @@
         <v>20</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="D6" s="28" t="n">
         <v>2</v>
@@ -4796,21 +4982,21 @@
         <v>44</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="J6" s="27" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="D7" s="28" t="n">
         <v>1</v>
@@ -4829,21 +5015,21 @@
         <v>22</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="D8" s="28" t="n">
         <v>2</v>
@@ -4862,21 +5048,21 @@
         <v>20</v>
       </c>
       <c r="I8" s="30" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="J8" s="27" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="D9" s="28" t="n">
         <v>2</v>
@@ -4895,21 +5081,21 @@
         <v>18</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="D10" s="28" t="n">
         <v>1</v>
@@ -4928,21 +5114,21 @@
         <v>40</v>
       </c>
       <c r="I10" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="J10" s="27" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D11" s="28" t="n">
         <v>1</v>
@@ -4961,21 +5147,21 @@
         <v>19</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="D12" s="28" t="n">
         <v>2</v>
@@ -4994,21 +5180,21 @@
         <v>18</v>
       </c>
       <c r="I12" s="30" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="J12" s="27" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="D13" s="28" t="n">
         <v>1</v>
@@ -5027,21 +5213,21 @@
         <v>18</v>
       </c>
       <c r="I13" s="30" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="D14" s="28" t="n">
         <v>2</v>
@@ -5060,21 +5246,21 @@
         <v>20</v>
       </c>
       <c r="I14" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="J14" s="27" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="D15" s="28" t="n">
         <v>1</v>
@@ -5093,21 +5279,21 @@
         <v>20</v>
       </c>
       <c r="I15" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="J15" s="27" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="D16" s="28" t="n">
         <v>2</v>
@@ -5126,21 +5312,21 @@
         <v>20</v>
       </c>
       <c r="I16" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="J16" s="27" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="D17" s="28" t="n">
         <v>1</v>
@@ -5159,21 +5345,21 @@
         <v>20</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="J17" s="27" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="D18" s="28" t="n">
         <v>1</v>
@@ -5192,21 +5378,21 @@
         <v>16</v>
       </c>
       <c r="I18" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="J18" s="27" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="D19" s="28" t="n">
         <v>1</v>
@@ -5225,21 +5411,21 @@
         <v>16</v>
       </c>
       <c r="I19" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="J19" s="27" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="D20" s="28" t="n">
         <v>2</v>
@@ -5258,21 +5444,21 @@
         <v>18</v>
       </c>
       <c r="I20" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="J20" s="27" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="D21" s="28" t="n">
         <v>1</v>
@@ -5291,21 +5477,21 @@
         <v>40</v>
       </c>
       <c r="I21" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="J21" s="27" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="D22" s="28" t="n">
         <v>1</v>
@@ -5324,21 +5510,21 @@
         <v>20</v>
       </c>
       <c r="I22" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="J22" s="27" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="D23" s="28" t="n">
         <v>1</v>
@@ -5357,21 +5543,21 @@
         <v>20</v>
       </c>
       <c r="I23" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="J23" s="27" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="26" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="D24" s="28" t="n">
         <v>1</v>
@@ -5390,21 +5576,21 @@
         <v>20</v>
       </c>
       <c r="I24" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="J24" s="27" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="26" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="D25" s="28" t="n">
         <v>1</v>
@@ -5423,21 +5609,21 @@
         <v>20</v>
       </c>
       <c r="I25" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="J25" s="27" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="26" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="D26" s="28" t="n">
         <v>1</v>
@@ -5456,21 +5642,21 @@
         <v>20</v>
       </c>
       <c r="I26" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="J26" s="27" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="26" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="D27" s="28" t="n">
         <v>1</v>
@@ -5489,21 +5675,21 @@
         <v>40</v>
       </c>
       <c r="I27" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="J27" s="27" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="26" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D28" s="28" t="n">
         <v>1</v>
@@ -5522,21 +5708,21 @@
         <v>18</v>
       </c>
       <c r="I28" s="30" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="J28" s="27" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="D29" s="28" t="n">
         <v>1</v>
@@ -5555,17 +5741,17 @@
         <v>18</v>
       </c>
       <c r="I29" s="30" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="J29" s="27" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="31"/>
       <c r="B30" s="31"/>
       <c r="C30" s="32" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="D30" s="31"/>
       <c r="E30" s="32" t="n">
@@ -5583,7 +5769,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -5597,10 +5783,10 @@
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="3" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
@@ -5612,10 +5798,10 @@
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="3" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
@@ -5627,10 +5813,10 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="3" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
@@ -5642,10 +5828,10 @@
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="3" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
@@ -5657,10 +5843,10 @@
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="3" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
@@ -5672,7 +5858,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -5686,10 +5872,10 @@
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="3" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="D41" s="11"/>
       <c r="E41" s="11"/>
@@ -5701,10 +5887,10 @@
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="3" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
@@ -5716,10 +5902,10 @@
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="3" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
@@ -5731,10 +5917,10 @@
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="3" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
@@ -5746,10 +5932,10 @@
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="3" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="D45" s="11"/>
       <c r="E45" s="11"/>
@@ -5761,10 +5947,10 @@
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="3" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="D46" s="11"/>
       <c r="E46" s="11"/>
@@ -5776,7 +5962,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -5790,22 +5976,22 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="12" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="H49" s="12"/>
       <c r="I49" s="12"/>
@@ -5813,22 +5999,22 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="26" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="C50" s="30" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="D50" s="30" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="E50" s="30" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="F50" s="30" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="G50" s="34" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="H50" s="34"/>
       <c r="I50" s="34"/>
@@ -5836,22 +6022,22 @@
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="26" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="C51" s="30" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="D51" s="30" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="E51" s="30" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="F51" s="30" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="G51" s="34" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="H51" s="34"/>
       <c r="I51" s="34"/>
@@ -5859,22 +6045,22 @@
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="26" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="C52" s="30" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="D52" s="30" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="E52" s="30" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="F52" s="30" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="G52" s="34" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="H52" s="34"/>
       <c r="I52" s="34"/>
@@ -5882,22 +6068,22 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="26" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="D53" s="30" t="s">
+        <v>468</v>
+      </c>
+      <c r="E53" s="30" t="s">
+        <v>469</v>
+      </c>
+      <c r="F53" s="30" t="s">
         <v>454</v>
       </c>
-      <c r="E53" s="30" t="s">
-        <v>455</v>
-      </c>
-      <c r="F53" s="30" t="s">
-        <v>440</v>
-      </c>
       <c r="G53" s="34" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="H53" s="34"/>
       <c r="I53" s="34"/>
@@ -5905,22 +6091,22 @@
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="26" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="C54" s="30" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="D54" s="30" t="s">
+        <v>468</v>
+      </c>
+      <c r="E54" s="30" t="s">
+        <v>472</v>
+      </c>
+      <c r="F54" s="30" t="s">
         <v>454</v>
       </c>
-      <c r="E54" s="30" t="s">
-        <v>458</v>
-      </c>
-      <c r="F54" s="30" t="s">
-        <v>440</v>
-      </c>
       <c r="G54" s="34" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="H54" s="34"/>
       <c r="I54" s="34"/>
@@ -5928,22 +6114,22 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="26" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="D55" s="30" t="s">
+        <v>468</v>
+      </c>
+      <c r="E55" s="30" t="s">
+        <v>475</v>
+      </c>
+      <c r="F55" s="30" t="s">
         <v>454</v>
       </c>
-      <c r="E55" s="30" t="s">
-        <v>461</v>
-      </c>
-      <c r="F55" s="30" t="s">
-        <v>440</v>
-      </c>
       <c r="G55" s="34" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="H55" s="34"/>
       <c r="I55" s="34"/>
@@ -5951,22 +6137,22 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="26" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="E56" s="30" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="F56" s="30" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="G56" s="34" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="H56" s="34"/>
       <c r="I56" s="34"/>
@@ -5974,22 +6160,22 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="26" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="D57" s="30" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="E57" s="30" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="F57" s="30" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="G57" s="34" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="H57" s="34"/>
       <c r="I57" s="34"/>
@@ -5997,22 +6183,22 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="26" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="D58" s="30" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="F58" s="30" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="G58" s="34" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="H58" s="34"/>
       <c r="I58" s="34"/>
@@ -6020,7 +6206,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -6034,14 +6220,14 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="26" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="C61" s="35" t="n">
         <f aca="false">SUMPRODUCT(F5:F50,E5:E50)</f>
         <v>408</v>
       </c>
       <c r="D61" s="36" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="E61" s="36"/>
       <c r="F61" s="36"/>
@@ -6052,14 +6238,14 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="26" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="C62" s="35" t="n">
         <f aca="false">SUMPRODUCT(G5:G50,E5:E50)</f>
         <v>157</v>
       </c>
       <c r="D62" s="36" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="E62" s="36"/>
       <c r="F62" s="36"/>
@@ -6070,14 +6256,14 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="26" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="C63" s="35" t="n">
         <f aca="false">SUM(H5:H50)</f>
         <v>1130</v>
       </c>
       <c r="D63" s="36" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="E63" s="36"/>
       <c r="F63" s="36"/>
@@ -6088,14 +6274,14 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="26" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="C64" s="37" t="n">
         <f aca="false">SUMPRODUCT(F5:F50,E5:E50)/SUM(H5:H50)</f>
         <v>0.361061946902655</v>
       </c>
       <c r="D64" s="36" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="E64" s="36"/>
       <c r="F64" s="36"/>
@@ -6106,13 +6292,13 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="26" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="C65" s="38" t="n">
         <v>60</v>
       </c>
       <c r="D65" s="36" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="E65" s="36"/>
       <c r="F65" s="36"/>
@@ -6123,13 +6309,13 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="26" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="C66" s="38" t="n">
         <v>10</v>
       </c>
       <c r="D66" s="36" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="E66" s="36"/>
       <c r="F66" s="36"/>
@@ -6200,7 +6386,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -6218,7 +6404,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6236,7 +6422,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -6251,42 +6437,42 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B6" s="39" t="str">
         <f aca="false">VLOOKUP(A6,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -6325,7 +6511,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B7" s="39" t="str">
         <f aca="false">VLOOKUP(A7,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -6364,7 +6550,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="B8" s="39" t="str">
         <f aca="false">VLOOKUP(A8,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -6403,7 +6589,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B9" s="39" t="str">
         <f aca="false">VLOOKUP(A9,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -6442,7 +6628,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="B10" s="39" t="str">
         <f aca="false">VLOOKUP(A10,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -6481,7 +6667,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="B11" s="39" t="str">
         <f aca="false">VLOOKUP(A11,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -6520,7 +6706,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B12" s="39" t="str">
         <f aca="false">VLOOKUP(A12,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -6559,7 +6745,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B13" s="39" t="str">
         <f aca="false">VLOOKUP(A13,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -6598,7 +6784,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B14" s="39" t="str">
         <f aca="false">VLOOKUP(A14,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -6637,7 +6823,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B15" s="39" t="str">
         <f aca="false">VLOOKUP(A15,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -6676,7 +6862,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B16" s="39" t="str">
         <f aca="false">VLOOKUP(A16,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -6715,7 +6901,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="B17" s="39" t="str">
         <f aca="false">VLOOKUP(A17,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -6754,7 +6940,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="B18" s="39" t="str">
         <f aca="false">VLOOKUP(A18,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -6793,7 +6979,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B19" s="39" t="str">
         <f aca="false">VLOOKUP(A19,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -6832,7 +7018,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="B20" s="39" t="str">
         <f aca="false">VLOOKUP(A20,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -6871,7 +7057,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="B21" s="39" t="str">
         <f aca="false">VLOOKUP(A21,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -6910,7 +7096,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="B22" s="39" t="str">
         <f aca="false">VLOOKUP(A22,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -6949,7 +7135,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="B23" s="39" t="str">
         <f aca="false">VLOOKUP(A23,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -6988,7 +7174,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="26" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="B24" s="39" t="str">
         <f aca="false">VLOOKUP(A24,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7027,7 +7213,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="26" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="B25" s="39" t="str">
         <f aca="false">VLOOKUP(A25,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7066,7 +7252,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="26" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B26" s="39" t="str">
         <f aca="false">VLOOKUP(A26,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7105,7 +7291,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="26" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="B27" s="39" t="str">
         <f aca="false">VLOOKUP(A27,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7144,7 +7330,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="26" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="B28" s="39" t="str">
         <f aca="false">VLOOKUP(A28,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7183,7 +7369,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="B29" s="39" t="str">
         <f aca="false">VLOOKUP(A29,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7222,7 +7408,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="26" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="B30" s="39" t="str">
         <f aca="false">VLOOKUP(A30,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7262,7 +7448,7 @@
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="31"/>
       <c r="B31" s="32" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="C31" s="42" t="n">
         <f aca="false">SUM(C6:C30)</f>
@@ -7303,7 +7489,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -7318,42 +7504,42 @@
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="26" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B36" s="39" t="str">
         <f aca="false">VLOOKUP(A36,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7394,7 +7580,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="26" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B37" s="39" t="str">
         <f aca="false">VLOOKUP(A37,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7435,7 +7621,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="26" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="B38" s="39" t="str">
         <f aca="false">VLOOKUP(A38,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7476,7 +7662,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="26" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B39" s="39" t="str">
         <f aca="false">VLOOKUP(A39,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7517,7 +7703,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="26" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="B40" s="39" t="str">
         <f aca="false">VLOOKUP(A40,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7558,7 +7744,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="26" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="B41" s="39" t="str">
         <f aca="false">VLOOKUP(A41,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7599,7 +7785,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="26" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B42" s="39" t="str">
         <f aca="false">VLOOKUP(A42,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7640,7 +7826,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="26" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B43" s="39" t="str">
         <f aca="false">VLOOKUP(A43,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7681,7 +7867,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="26" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B44" s="39" t="str">
         <f aca="false">VLOOKUP(A44,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7722,7 +7908,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="26" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B45" s="39" t="str">
         <f aca="false">VLOOKUP(A45,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7763,7 +7949,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="26" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B46" s="39" t="str">
         <f aca="false">VLOOKUP(A46,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7804,7 +7990,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="26" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="B47" s="39" t="str">
         <f aca="false">VLOOKUP(A47,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7845,7 +8031,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="26" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="B48" s="39" t="str">
         <f aca="false">VLOOKUP(A48,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7886,7 +8072,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="26" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B49" s="39" t="str">
         <f aca="false">VLOOKUP(A49,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7927,7 +8113,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="26" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="B50" s="39" t="str">
         <f aca="false">VLOOKUP(A50,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -7968,7 +8154,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="26" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="B51" s="39" t="str">
         <f aca="false">VLOOKUP(A51,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -8009,7 +8195,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="26" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="B52" s="39" t="str">
         <f aca="false">VLOOKUP(A52,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -8050,7 +8236,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="26" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="B53" s="39" t="str">
         <f aca="false">VLOOKUP(A53,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -8091,7 +8277,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="26" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="B54" s="39" t="str">
         <f aca="false">VLOOKUP(A54,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -8132,7 +8318,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="26" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="B55" s="39" t="str">
         <f aca="false">VLOOKUP(A55,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -8173,7 +8359,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="26" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B56" s="39" t="str">
         <f aca="false">VLOOKUP(A56,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -8214,7 +8400,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="26" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="B57" s="39" t="str">
         <f aca="false">VLOOKUP(A57,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -8255,7 +8441,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="26" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="B58" s="39" t="str">
         <f aca="false">VLOOKUP(A58,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -8296,7 +8482,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="26" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="B59" s="39" t="str">
         <f aca="false">VLOOKUP(A59,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -8337,7 +8523,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="26" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="B60" s="39" t="str">
         <f aca="false">VLOOKUP(A60,ACTIVIDADES!$A$5:$B$50,2,FALSE())</f>
@@ -8379,7 +8565,7 @@
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="31"/>
       <c r="B61" s="32" t="s">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="C61" s="42" t="n">
         <f aca="false">SUM(C36:C60)</f>
@@ -8420,7 +8606,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -8432,36 +8618,36 @@
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="B65" s="12" t="s">
         <v>48</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="D65" s="12" t="s">
+        <v>520</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="F65" s="12" t="s">
         <v>506</v>
       </c>
-      <c r="E65" s="12" t="s">
+      <c r="G65" s="12" t="s">
         <v>507</v>
       </c>
-      <c r="F65" s="12" t="s">
-        <v>492</v>
-      </c>
-      <c r="G65" s="12" t="s">
-        <v>493</v>
-      </c>
       <c r="H65" s="12" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="26" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B66" s="27" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="C66" s="28" t="n">
         <v>4</v>
@@ -8488,10 +8674,10 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="26" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="C67" s="28" t="n">
         <v>3</v>
@@ -8519,7 +8705,7 @@
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="31"/>
       <c r="B68" s="32" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="C68" s="42" t="n">
         <f aca="false">SUM(C66:C67)</f>
@@ -8548,7 +8734,7 @@
     </row>
     <row r="71" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -8560,36 +8746,36 @@
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>48</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="D72" s="12" t="s">
+        <v>520</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="F72" s="12" t="s">
         <v>506</v>
       </c>
-      <c r="E72" s="12" t="s">
+      <c r="G72" s="12" t="s">
         <v>507</v>
       </c>
-      <c r="F72" s="12" t="s">
-        <v>492</v>
-      </c>
-      <c r="G72" s="12" t="s">
-        <v>493</v>
-      </c>
       <c r="H72" s="12" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="26" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B73" s="27" t="s">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="C73" s="28" t="n">
         <v>15</v>
@@ -8616,10 +8802,10 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="26" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B74" s="27" t="s">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="C74" s="28" t="n">
         <v>9</v>
@@ -8646,10 +8832,10 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="26" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="B75" s="27" t="s">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="C75" s="28" t="n">
         <v>9</v>
@@ -8676,10 +8862,10 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="26" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B76" s="27" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="C76" s="28" t="n">
         <v>8</v>
@@ -8707,7 +8893,7 @@
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="31"/>
       <c r="B77" s="32" t="s">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="C77" s="42" t="n">
         <f aca="false">SUM(C73:C76)</f>
@@ -8736,7 +8922,7 @@
     </row>
     <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -8748,39 +8934,39 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="E81" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="F81" s="12" t="s">
         <v>521</v>
-      </c>
-      <c r="F81" s="12" t="s">
-        <v>507</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>54</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>522</v>
+        <v>536</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="27" t="s">
-        <v>523</v>
+        <v>537</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="C82" s="30" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="D82" s="28" t="n">
         <v>32</v>
@@ -8804,13 +8990,13 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="27" t="s">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="B83" s="30" t="s">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="C83" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="D83" s="28" t="n">
         <v>25</v>
@@ -8834,13 +9020,13 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="27" t="s">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="B84" s="30" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="C84" s="30" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="D84" s="28" t="n">
         <v>32</v>
@@ -8864,13 +9050,13 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="27" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="B85" s="30" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="C85" s="30" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="D85" s="28" t="n">
         <v>25</v>
@@ -8895,7 +9081,7 @@
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="31"/>
       <c r="B86" s="32" t="s">
-        <v>529</v>
+        <v>543</v>
       </c>
       <c r="C86" s="31"/>
       <c r="D86" s="42" t="n">
@@ -8952,7 +9138,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>530</v>
+        <v>544</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -8974,7 +9160,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8996,63 +9182,63 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>533</v>
+        <v>547</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>535</v>
+        <v>549</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>536</v>
+        <v>550</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>537</v>
+        <v>551</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>541</v>
+        <v>555</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>542</v>
+        <v>556</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>545</v>
+        <v>559</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B5" s="30" t="n">
         <v>1</v>
@@ -9087,39 +9273,39 @@
         <v>0</v>
       </c>
       <c r="K5" s="40" t="n">
-        <f aca="false">H5*(J5*manut_dia+(C5-J5)*manut_med)</f>
-        <v>411.4</v>
+        <f aca="false">H5*(J5*manut_dia_copr+(C5-J5)*manut_med_copr)</f>
+        <v>330</v>
       </c>
       <c r="L5" s="40" t="n">
-        <f aca="false">I5*J5*alojamiento</f>
+        <f aca="false">I5*J5*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M5" s="40" t="n">
-        <f aca="false">C5*bus_dia*CEILING(I5/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C5*MIN(CEILING(I5/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>114.4</v>
       </c>
       <c r="N5" s="41" t="n">
         <f aca="false">K5+L5+M5</f>
-        <v>1111.4</v>
+        <v>444.4</v>
       </c>
       <c r="O5" s="48" t="n">
         <v>0.4</v>
       </c>
       <c r="P5" s="40" t="n">
         <f aca="false">N5*O5</f>
-        <v>444.56</v>
+        <v>177.76</v>
       </c>
       <c r="Q5" s="40" t="n">
         <f aca="false">N5*(1-O5)</f>
-        <v>666.84</v>
+        <v>266.64</v>
       </c>
       <c r="R5" s="28" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B6" s="30" t="n">
         <v>1</v>
@@ -9154,39 +9340,39 @@
         <v>1</v>
       </c>
       <c r="K6" s="40" t="n">
-        <f aca="false">H6*(J6*manut_dia+(C6-J6)*manut_med)</f>
-        <v>1346.4</v>
+        <f aca="false">H6*(J6*manut_dia_copr+(C6-J6)*manut_med_copr)</f>
+        <v>1080</v>
       </c>
       <c r="L6" s="40" t="n">
-        <f aca="false">I6*J6*alojamiento</f>
-        <v>1517.31</v>
+        <f aca="false">I6*J6*alojamiento_copr</f>
+        <v>1265</v>
       </c>
       <c r="M6" s="40" t="n">
-        <f aca="false">C6*bus_dia*CEILING(I6/cap_bus,1)</f>
-        <v>1400</v>
+        <f aca="false">C6*MIN(CEILING(I6/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>228.8</v>
       </c>
       <c r="N6" s="41" t="n">
         <f aca="false">K6+L6+M6</f>
-        <v>4263.71</v>
+        <v>2573.8</v>
       </c>
       <c r="O6" s="48" t="n">
         <v>0.7</v>
       </c>
       <c r="P6" s="40" t="n">
         <f aca="false">N6*O6</f>
-        <v>2984.597</v>
+        <v>1801.66</v>
       </c>
       <c r="Q6" s="40" t="n">
         <f aca="false">N6*(1-O6)</f>
-        <v>1279.113</v>
+        <v>772.14</v>
       </c>
       <c r="R6" s="28" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B7" s="30" t="n">
         <v>2</v>
@@ -9221,39 +9407,39 @@
         <v>1</v>
       </c>
       <c r="K7" s="40" t="n">
-        <f aca="false">H7*(J7*manut_dia+(C7-J7)*manut_med)</f>
-        <v>1346.4</v>
+        <f aca="false">H7*(J7*manut_dia_copr+(C7-J7)*manut_med_copr)</f>
+        <v>1080</v>
       </c>
       <c r="L7" s="40" t="n">
-        <f aca="false">I7*J7*alojamiento</f>
-        <v>1517.31</v>
+        <f aca="false">I7*J7*alojamiento_copr</f>
+        <v>1265</v>
       </c>
       <c r="M7" s="40" t="n">
-        <f aca="false">C7*bus_dia*CEILING(I7/cap_bus,1)</f>
-        <v>1400</v>
+        <f aca="false">C7*MIN(CEILING(I7/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>228.8</v>
       </c>
       <c r="N7" s="41" t="n">
         <f aca="false">K7+L7+M7</f>
-        <v>4263.71</v>
+        <v>2573.8</v>
       </c>
       <c r="O7" s="48" t="n">
         <v>0.7</v>
       </c>
       <c r="P7" s="40" t="n">
         <f aca="false">N7*O7</f>
-        <v>2984.597</v>
+        <v>1801.66</v>
       </c>
       <c r="Q7" s="40" t="n">
         <f aca="false">N7*(1-O7)</f>
-        <v>1279.113</v>
+        <v>772.14</v>
       </c>
       <c r="R7" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="B8" s="30" t="n">
         <v>1</v>
@@ -9288,39 +9474,39 @@
         <v>0</v>
       </c>
       <c r="K8" s="40" t="n">
-        <f aca="false">H8*(J8*manut_dia+(C8-J8)*manut_med)</f>
-        <v>448.8</v>
+        <f aca="false">H8*(J8*manut_dia_copr+(C8-J8)*manut_med_copr)</f>
+        <v>360</v>
       </c>
       <c r="L8" s="40" t="n">
-        <f aca="false">I8*J8*alojamiento</f>
+        <f aca="false">I8*J8*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M8" s="40" t="n">
-        <f aca="false">C8*bus_dia*CEILING(I8/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C8*MIN(CEILING(I8/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>114.4</v>
       </c>
       <c r="N8" s="41" t="n">
         <f aca="false">K8+L8+M8</f>
-        <v>1148.8</v>
+        <v>474.4</v>
       </c>
       <c r="O8" s="48" t="n">
         <v>0.7</v>
       </c>
       <c r="P8" s="40" t="n">
         <f aca="false">N8*O8</f>
-        <v>804.16</v>
+        <v>332.08</v>
       </c>
       <c r="Q8" s="40" t="n">
         <f aca="false">N8*(1-O8)</f>
-        <v>344.64</v>
+        <v>142.32</v>
       </c>
       <c r="R8" s="28" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B9" s="30" t="n">
         <v>1</v>
@@ -9355,39 +9541,39 @@
         <v>1</v>
       </c>
       <c r="K9" s="40" t="n">
-        <f aca="false">H9*(J9*manut_dia+(C9-J9)*manut_med)</f>
-        <v>1234.2</v>
+        <f aca="false">H9*(J9*manut_dia_copr+(C9-J9)*manut_med_copr)</f>
+        <v>990</v>
       </c>
       <c r="L9" s="40" t="n">
-        <f aca="false">I9*J9*alojamiento</f>
-        <v>1385.37</v>
+        <f aca="false">I9*J9*alojamiento_copr</f>
+        <v>1155</v>
       </c>
       <c r="M9" s="40" t="n">
-        <f aca="false">C9*bus_dia*CEILING(I9/cap_bus,1)</f>
-        <v>1400</v>
+        <f aca="false">C9*MIN(CEILING(I9/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>228.8</v>
       </c>
       <c r="N9" s="41" t="n">
         <f aca="false">K9+L9+M9</f>
-        <v>4019.57</v>
+        <v>2373.8</v>
       </c>
       <c r="O9" s="48" t="n">
         <v>0.7</v>
       </c>
       <c r="P9" s="40" t="n">
         <f aca="false">N9*O9</f>
-        <v>2813.699</v>
+        <v>1661.66</v>
       </c>
       <c r="Q9" s="40" t="n">
         <f aca="false">N9*(1-O9)</f>
-        <v>1205.871</v>
+        <v>712.14</v>
       </c>
       <c r="R9" s="28" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="B10" s="30" t="n">
         <v>1</v>
@@ -9422,39 +9608,39 @@
         <v>1</v>
       </c>
       <c r="K10" s="40" t="n">
-        <f aca="false">H10*(J10*manut_dia+(C10-J10)*manut_med)</f>
-        <v>1178.1</v>
+        <f aca="false">H10*(J10*manut_dia_copr+(C10-J10)*manut_med_copr)</f>
+        <v>945</v>
       </c>
       <c r="L10" s="40" t="n">
-        <f aca="false">I10*J10*alojamiento</f>
-        <v>1319.4</v>
+        <f aca="false">I10*J10*alojamiento_copr</f>
+        <v>1100</v>
       </c>
       <c r="M10" s="40" t="n">
-        <f aca="false">C10*bus_dia*CEILING(I10/cap_bus,1)</f>
-        <v>1400</v>
+        <f aca="false">C10*MIN(CEILING(I10/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>114.4</v>
       </c>
       <c r="N10" s="41" t="n">
         <f aca="false">K10+L10+M10</f>
-        <v>3897.5</v>
+        <v>2159.4</v>
       </c>
       <c r="O10" s="48" t="n">
         <v>0.6</v>
       </c>
       <c r="P10" s="40" t="n">
         <f aca="false">N10*O10</f>
-        <v>2338.5</v>
+        <v>1295.64</v>
       </c>
       <c r="Q10" s="40" t="n">
         <f aca="false">N10*(1-O10)</f>
-        <v>1559</v>
+        <v>863.76</v>
       </c>
       <c r="R10" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="B11" s="30" t="n">
         <v>1</v>
@@ -9489,39 +9675,39 @@
         <v>0</v>
       </c>
       <c r="K11" s="40" t="n">
-        <f aca="false">H11*(J11*manut_dia+(C11-J11)*manut_med)</f>
-        <v>411.4</v>
+        <f aca="false">H11*(J11*manut_dia_copr+(C11-J11)*manut_med_copr)</f>
+        <v>330</v>
       </c>
       <c r="L11" s="40" t="n">
-        <f aca="false">I11*J11*alojamiento</f>
+        <f aca="false">I11*J11*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M11" s="40" t="n">
-        <f aca="false">C11*bus_dia*CEILING(I11/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C11*MIN(CEILING(I11/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>114.4</v>
       </c>
       <c r="N11" s="41" t="n">
         <f aca="false">K11+L11+M11</f>
-        <v>1111.4</v>
+        <v>444.4</v>
       </c>
       <c r="O11" s="48" t="n">
         <v>0.6</v>
       </c>
       <c r="P11" s="40" t="n">
         <f aca="false">N11*O11</f>
-        <v>666.84</v>
+        <v>266.64</v>
       </c>
       <c r="Q11" s="40" t="n">
         <f aca="false">N11*(1-O11)</f>
-        <v>444.56</v>
+        <v>177.76</v>
       </c>
       <c r="R11" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="B12" s="30" t="n">
         <v>2</v>
@@ -9556,39 +9742,39 @@
         <v>0</v>
       </c>
       <c r="K12" s="40" t="n">
-        <f aca="false">H12*(J12*manut_dia+(C12-J12)*manut_med)</f>
-        <v>411.4</v>
+        <f aca="false">H12*(J12*manut_dia_copr+(C12-J12)*manut_med_copr)</f>
+        <v>330</v>
       </c>
       <c r="L12" s="40" t="n">
-        <f aca="false">I12*J12*alojamiento</f>
+        <f aca="false">I12*J12*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M12" s="40" t="n">
-        <f aca="false">C12*bus_dia*CEILING(I12/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C12*MIN(CEILING(I12/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>114.4</v>
       </c>
       <c r="N12" s="41" t="n">
         <f aca="false">K12+L12+M12</f>
-        <v>1111.4</v>
+        <v>444.4</v>
       </c>
       <c r="O12" s="48" t="n">
         <v>0.6</v>
       </c>
       <c r="P12" s="40" t="n">
         <f aca="false">N12*O12</f>
-        <v>666.84</v>
+        <v>266.64</v>
       </c>
       <c r="Q12" s="40" t="n">
         <f aca="false">N12*(1-O12)</f>
-        <v>444.56</v>
+        <v>177.76</v>
       </c>
       <c r="R12" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B13" s="30" t="n">
         <v>1</v>
@@ -9623,39 +9809,39 @@
         <v>0</v>
       </c>
       <c r="K13" s="40" t="n">
-        <f aca="false">H13*(J13*manut_dia+(C13-J13)*manut_med)</f>
-        <v>392.7</v>
+        <f aca="false">H13*(J13*manut_dia_copr+(C13-J13)*manut_med_copr)</f>
+        <v>315</v>
       </c>
       <c r="L13" s="40" t="n">
-        <f aca="false">I13*J13*alojamiento</f>
+        <f aca="false">I13*J13*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M13" s="40" t="n">
-        <f aca="false">C13*bus_dia*CEILING(I13/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C13*MIN(CEILING(I13/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>57.2</v>
       </c>
       <c r="N13" s="41" t="n">
         <f aca="false">K13+L13+M13</f>
-        <v>1092.7</v>
+        <v>372.2</v>
       </c>
       <c r="O13" s="48" t="n">
         <v>0.6</v>
       </c>
       <c r="P13" s="40" t="n">
         <f aca="false">N13*O13</f>
-        <v>655.62</v>
+        <v>223.32</v>
       </c>
       <c r="Q13" s="40" t="n">
         <f aca="false">N13*(1-O13)</f>
-        <v>437.08</v>
+        <v>148.88</v>
       </c>
       <c r="R13" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B14" s="30" t="n">
         <v>1</v>
@@ -9690,39 +9876,39 @@
         <v>1</v>
       </c>
       <c r="K14" s="40" t="n">
-        <f aca="false">H14*(J14*manut_dia+(C14-J14)*manut_med)</f>
-        <v>1122</v>
+        <f aca="false">H14*(J14*manut_dia_copr+(C14-J14)*manut_med_copr)</f>
+        <v>900</v>
       </c>
       <c r="L14" s="40" t="n">
-        <f aca="false">I14*J14*alojamiento</f>
-        <v>1253.43</v>
+        <f aca="false">I14*J14*alojamiento_copr</f>
+        <v>1045</v>
       </c>
       <c r="M14" s="40" t="n">
-        <f aca="false">C14*bus_dia*CEILING(I14/cap_bus,1)</f>
-        <v>1400</v>
+        <f aca="false">C14*MIN(CEILING(I14/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>114.4</v>
       </c>
       <c r="N14" s="41" t="n">
         <f aca="false">K14+L14+M14</f>
-        <v>3775.43</v>
+        <v>2059.4</v>
       </c>
       <c r="O14" s="48" t="n">
         <v>0.7</v>
       </c>
       <c r="P14" s="40" t="n">
         <f aca="false">N14*O14</f>
-        <v>2642.801</v>
+        <v>1441.58</v>
       </c>
       <c r="Q14" s="40" t="n">
         <f aca="false">N14*(1-O14)</f>
-        <v>1132.629</v>
+        <v>617.82</v>
       </c>
       <c r="R14" s="28" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B15" s="30" t="n">
         <v>1</v>
@@ -9757,39 +9943,39 @@
         <v>0</v>
       </c>
       <c r="K15" s="40" t="n">
-        <f aca="false">H15*(J15*manut_dia+(C15-J15)*manut_med)</f>
-        <v>374</v>
+        <f aca="false">H15*(J15*manut_dia_copr+(C15-J15)*manut_med_copr)</f>
+        <v>300</v>
       </c>
       <c r="L15" s="40" t="n">
-        <f aca="false">I15*J15*alojamiento</f>
+        <f aca="false">I15*J15*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M15" s="40" t="n">
-        <f aca="false">C15*bus_dia*CEILING(I15/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C15*MIN(CEILING(I15/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>57.2</v>
       </c>
       <c r="N15" s="41" t="n">
         <f aca="false">K15+L15+M15</f>
-        <v>1074</v>
+        <v>357.2</v>
       </c>
       <c r="O15" s="48" t="n">
         <v>0.7</v>
       </c>
       <c r="P15" s="40" t="n">
         <f aca="false">N15*O15</f>
-        <v>751.8</v>
+        <v>250.04</v>
       </c>
       <c r="Q15" s="40" t="n">
         <f aca="false">N15*(1-O15)</f>
-        <v>322.2</v>
+        <v>107.16</v>
       </c>
       <c r="R15" s="28" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B16" s="30" t="n">
         <v>1</v>
@@ -9824,39 +10010,39 @@
         <v>1</v>
       </c>
       <c r="K16" s="40" t="n">
-        <f aca="false">H16*(J16*manut_dia+(C16-J16)*manut_med)</f>
-        <v>1290.3</v>
+        <f aca="false">H16*(J16*manut_dia_copr+(C16-J16)*manut_med_copr)</f>
+        <v>1035</v>
       </c>
       <c r="L16" s="40" t="n">
-        <f aca="false">I16*J16*alojamiento</f>
-        <v>1385.37</v>
+        <f aca="false">I16*J16*alojamiento_copr</f>
+        <v>1155</v>
       </c>
       <c r="M16" s="40" t="n">
-        <f aca="false">C16*bus_dia*CEILING(I16/cap_bus,1)</f>
-        <v>1400</v>
+        <f aca="false">C16*MIN(CEILING(I16/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>228.8</v>
       </c>
       <c r="N16" s="41" t="n">
         <f aca="false">K16+L16+M16</f>
-        <v>4075.67</v>
+        <v>2418.8</v>
       </c>
       <c r="O16" s="48" t="n">
         <v>0.4</v>
       </c>
       <c r="P16" s="40" t="n">
         <f aca="false">N16*O16</f>
-        <v>1630.268</v>
+        <v>967.52</v>
       </c>
       <c r="Q16" s="40" t="n">
         <f aca="false">N16*(1-O16)</f>
-        <v>2445.402</v>
+        <v>1451.28</v>
       </c>
       <c r="R16" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B17" s="30" t="n">
         <v>1</v>
@@ -9891,39 +10077,39 @@
         <v>0</v>
       </c>
       <c r="K17" s="40" t="n">
-        <f aca="false">H17*(J17*manut_dia+(C17-J17)*manut_med)</f>
-        <v>430.1</v>
+        <f aca="false">H17*(J17*manut_dia_copr+(C17-J17)*manut_med_copr)</f>
+        <v>345</v>
       </c>
       <c r="L17" s="40" t="n">
-        <f aca="false">I17*J17*alojamiento</f>
+        <f aca="false">I17*J17*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M17" s="40" t="n">
-        <f aca="false">C17*bus_dia*CEILING(I17/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C17*MIN(CEILING(I17/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>114.4</v>
       </c>
       <c r="N17" s="41" t="n">
         <f aca="false">K17+L17+M17</f>
-        <v>1130.1</v>
+        <v>459.4</v>
       </c>
       <c r="O17" s="48" t="n">
         <v>0.4</v>
       </c>
       <c r="P17" s="40" t="n">
         <f aca="false">N17*O17</f>
-        <v>452.04</v>
+        <v>183.76</v>
       </c>
       <c r="Q17" s="40" t="n">
         <f aca="false">N17*(1-O17)</f>
-        <v>678.06</v>
+        <v>275.64</v>
       </c>
       <c r="R17" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="B18" s="30" t="n">
         <v>1</v>
@@ -9958,39 +10144,39 @@
         <v>1</v>
       </c>
       <c r="K18" s="40" t="n">
-        <f aca="false">H18*(J18*manut_dia+(C18-J18)*manut_med)</f>
-        <v>1290.3</v>
+        <f aca="false">H18*(J18*manut_dia_copr+(C18-J18)*manut_med_copr)</f>
+        <v>1035</v>
       </c>
       <c r="L18" s="40" t="n">
-        <f aca="false">I18*J18*alojamiento</f>
-        <v>1385.37</v>
+        <f aca="false">I18*J18*alojamiento_copr</f>
+        <v>1155</v>
       </c>
       <c r="M18" s="40" t="n">
-        <f aca="false">C18*bus_dia*CEILING(I18/cap_bus,1)</f>
-        <v>1400</v>
+        <f aca="false">C18*MIN(CEILING(I18/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>228.8</v>
       </c>
       <c r="N18" s="41" t="n">
         <f aca="false">K18+L18+M18</f>
-        <v>4075.67</v>
+        <v>2418.8</v>
       </c>
       <c r="O18" s="48" t="n">
         <v>0.4</v>
       </c>
       <c r="P18" s="40" t="n">
         <f aca="false">N18*O18</f>
-        <v>1630.268</v>
+        <v>967.52</v>
       </c>
       <c r="Q18" s="40" t="n">
         <f aca="false">N18*(1-O18)</f>
-        <v>2445.402</v>
+        <v>1451.28</v>
       </c>
       <c r="R18" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="B19" s="30" t="n">
         <v>1</v>
@@ -10025,39 +10211,39 @@
         <v>0</v>
       </c>
       <c r="K19" s="40" t="n">
-        <f aca="false">H19*(J19*manut_dia+(C19-J19)*manut_med)</f>
-        <v>411.4</v>
+        <f aca="false">H19*(J19*manut_dia_copr+(C19-J19)*manut_med_copr)</f>
+        <v>330</v>
       </c>
       <c r="L19" s="40" t="n">
-        <f aca="false">I19*J19*alojamiento</f>
+        <f aca="false">I19*J19*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M19" s="40" t="n">
-        <f aca="false">C19*bus_dia*CEILING(I19/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C19*MIN(CEILING(I19/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>114.4</v>
       </c>
       <c r="N19" s="41" t="n">
         <f aca="false">K19+L19+M19</f>
-        <v>1111.4</v>
+        <v>444.4</v>
       </c>
       <c r="O19" s="48" t="n">
         <v>0.4</v>
       </c>
       <c r="P19" s="40" t="n">
         <f aca="false">N19*O19</f>
-        <v>444.56</v>
+        <v>177.76</v>
       </c>
       <c r="Q19" s="40" t="n">
         <f aca="false">N19*(1-O19)</f>
-        <v>666.84</v>
+        <v>266.64</v>
       </c>
       <c r="R19" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B20" s="30" t="n">
         <v>1</v>
@@ -10092,39 +10278,39 @@
         <v>0</v>
       </c>
       <c r="K20" s="40" t="n">
-        <f aca="false">H20*(J20*manut_dia+(C20-J20)*manut_med)</f>
-        <v>336.6</v>
+        <f aca="false">H20*(J20*manut_dia_copr+(C20-J20)*manut_med_copr)</f>
+        <v>270</v>
       </c>
       <c r="L20" s="40" t="n">
-        <f aca="false">I20*J20*alojamiento</f>
+        <f aca="false">I20*J20*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M20" s="40" t="n">
-        <f aca="false">C20*bus_dia*CEILING(I20/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C20*MIN(CEILING(I20/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>57.2</v>
       </c>
       <c r="N20" s="41" t="n">
         <f aca="false">K20+L20+M20</f>
-        <v>1036.6</v>
+        <v>327.2</v>
       </c>
       <c r="O20" s="48" t="n">
         <v>0.5</v>
       </c>
       <c r="P20" s="40" t="n">
         <f aca="false">N20*O20</f>
-        <v>518.3</v>
+        <v>163.6</v>
       </c>
       <c r="Q20" s="40" t="n">
         <f aca="false">N20*(1-O20)</f>
-        <v>518.3</v>
+        <v>163.6</v>
       </c>
       <c r="R20" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="B21" s="30" t="n">
         <v>1</v>
@@ -10159,39 +10345,39 @@
         <v>0</v>
       </c>
       <c r="K21" s="40" t="n">
-        <f aca="false">H21*(J21*manut_dia+(C21-J21)*manut_med)</f>
-        <v>336.6</v>
+        <f aca="false">H21*(J21*manut_dia_copr+(C21-J21)*manut_med_copr)</f>
+        <v>270</v>
       </c>
       <c r="L21" s="40" t="n">
-        <f aca="false">I21*J21*alojamiento</f>
+        <f aca="false">I21*J21*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M21" s="40" t="n">
-        <f aca="false">C21*bus_dia*CEILING(I21/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C21*MIN(CEILING(I21/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>57.2</v>
       </c>
       <c r="N21" s="41" t="n">
         <f aca="false">K21+L21+M21</f>
-        <v>1036.6</v>
+        <v>327.2</v>
       </c>
       <c r="O21" s="48" t="n">
         <v>0.5</v>
       </c>
       <c r="P21" s="40" t="n">
         <f aca="false">N21*O21</f>
-        <v>518.3</v>
+        <v>163.6</v>
       </c>
       <c r="Q21" s="40" t="n">
         <f aca="false">N21*(1-O21)</f>
-        <v>518.3</v>
+        <v>163.6</v>
       </c>
       <c r="R21" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="B22" s="30" t="n">
         <v>1</v>
@@ -10226,39 +10412,39 @@
         <v>1</v>
       </c>
       <c r="K22" s="40" t="n">
-        <f aca="false">H22*(J22*manut_dia+(C22-J22)*manut_med)</f>
-        <v>1178.1</v>
+        <f aca="false">H22*(J22*manut_dia_copr+(C22-J22)*manut_med_copr)</f>
+        <v>945</v>
       </c>
       <c r="L22" s="40" t="n">
-        <f aca="false">I22*J22*alojamiento</f>
-        <v>1319.4</v>
+        <f aca="false">I22*J22*alojamiento_copr</f>
+        <v>1100</v>
       </c>
       <c r="M22" s="40" t="n">
-        <f aca="false">C22*bus_dia*CEILING(I22/cap_bus,1)</f>
-        <v>1400</v>
+        <f aca="false">C22*MIN(CEILING(I22/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>114.4</v>
       </c>
       <c r="N22" s="41" t="n">
         <f aca="false">K22+L22+M22</f>
-        <v>3897.5</v>
+        <v>2159.4</v>
       </c>
       <c r="O22" s="48" t="n">
         <v>0.6</v>
       </c>
       <c r="P22" s="40" t="n">
         <f aca="false">N22*O22</f>
-        <v>2338.5</v>
+        <v>1295.64</v>
       </c>
       <c r="Q22" s="40" t="n">
         <f aca="false">N22*(1-O22)</f>
-        <v>1559</v>
+        <v>863.76</v>
       </c>
       <c r="R22" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="B23" s="30" t="n">
         <v>1</v>
@@ -10293,39 +10479,39 @@
         <v>0</v>
       </c>
       <c r="K23" s="40" t="n">
-        <f aca="false">H23*(J23*manut_dia+(C23-J23)*manut_med)</f>
-        <v>411.4</v>
+        <f aca="false">H23*(J23*manut_dia_copr+(C23-J23)*manut_med_copr)</f>
+        <v>330</v>
       </c>
       <c r="L23" s="40" t="n">
-        <f aca="false">I23*J23*alojamiento</f>
+        <f aca="false">I23*J23*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M23" s="40" t="n">
-        <f aca="false">C23*bus_dia*CEILING(I23/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C23*MIN(CEILING(I23/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>114.4</v>
       </c>
       <c r="N23" s="41" t="n">
         <f aca="false">K23+L23+M23</f>
-        <v>1111.4</v>
+        <v>444.4</v>
       </c>
       <c r="O23" s="48" t="n">
         <v>0.6</v>
       </c>
       <c r="P23" s="40" t="n">
         <f aca="false">N23*O23</f>
-        <v>666.84</v>
+        <v>266.64</v>
       </c>
       <c r="Q23" s="40" t="n">
         <f aca="false">N23*(1-O23)</f>
-        <v>444.56</v>
+        <v>177.76</v>
       </c>
       <c r="R23" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="26" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="B24" s="30" t="n">
         <v>2</v>
@@ -10360,39 +10546,39 @@
         <v>0</v>
       </c>
       <c r="K24" s="40" t="n">
-        <f aca="false">H24*(J24*manut_dia+(C24-J24)*manut_med)</f>
-        <v>411.4</v>
+        <f aca="false">H24*(J24*manut_dia_copr+(C24-J24)*manut_med_copr)</f>
+        <v>330</v>
       </c>
       <c r="L24" s="40" t="n">
-        <f aca="false">I24*J24*alojamiento</f>
+        <f aca="false">I24*J24*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M24" s="40" t="n">
-        <f aca="false">C24*bus_dia*CEILING(I24/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C24*MIN(CEILING(I24/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>114.4</v>
       </c>
       <c r="N24" s="41" t="n">
         <f aca="false">K24+L24+M24</f>
-        <v>1111.4</v>
+        <v>444.4</v>
       </c>
       <c r="O24" s="48" t="n">
         <v>0.6</v>
       </c>
       <c r="P24" s="40" t="n">
         <f aca="false">N24*O24</f>
-        <v>666.84</v>
+        <v>266.64</v>
       </c>
       <c r="Q24" s="40" t="n">
         <f aca="false">N24*(1-O24)</f>
-        <v>444.56</v>
+        <v>177.76</v>
       </c>
       <c r="R24" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="26" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="B25" s="30" t="n">
         <v>1</v>
@@ -10427,39 +10613,39 @@
         <v>0</v>
       </c>
       <c r="K25" s="40" t="n">
-        <f aca="false">H25*(J25*manut_dia+(C25-J25)*manut_med)</f>
-        <v>411.4</v>
+        <f aca="false">H25*(J25*manut_dia_copr+(C25-J25)*manut_med_copr)</f>
+        <v>330</v>
       </c>
       <c r="L25" s="40" t="n">
-        <f aca="false">I25*J25*alojamiento</f>
+        <f aca="false">I25*J25*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M25" s="40" t="n">
-        <f aca="false">C25*bus_dia*CEILING(I25/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C25*MIN(CEILING(I25/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>114.4</v>
       </c>
       <c r="N25" s="41" t="n">
         <f aca="false">K25+L25+M25</f>
-        <v>1111.4</v>
+        <v>444.4</v>
       </c>
       <c r="O25" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="P25" s="40" t="n">
         <f aca="false">N25*O25</f>
-        <v>333.42</v>
+        <v>133.32</v>
       </c>
       <c r="Q25" s="40" t="n">
         <f aca="false">N25*(1-O25)</f>
-        <v>777.98</v>
+        <v>311.08</v>
       </c>
       <c r="R25" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="26" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="B26" s="30" t="n">
         <v>1</v>
@@ -10494,39 +10680,39 @@
         <v>0</v>
       </c>
       <c r="K26" s="40" t="n">
-        <f aca="false">H26*(J26*manut_dia+(C26-J26)*manut_med)</f>
-        <v>411.4</v>
+        <f aca="false">H26*(J26*manut_dia_copr+(C26-J26)*manut_med_copr)</f>
+        <v>330</v>
       </c>
       <c r="L26" s="40" t="n">
-        <f aca="false">I26*J26*alojamiento</f>
+        <f aca="false">I26*J26*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M26" s="40" t="n">
-        <f aca="false">C26*bus_dia*CEILING(I26/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C26*MIN(CEILING(I26/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>114.4</v>
       </c>
       <c r="N26" s="41" t="n">
         <f aca="false">K26+L26+M26</f>
-        <v>1111.4</v>
+        <v>444.4</v>
       </c>
       <c r="O26" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="P26" s="40" t="n">
         <f aca="false">N26*O26</f>
-        <v>333.42</v>
+        <v>133.32</v>
       </c>
       <c r="Q26" s="40" t="n">
         <f aca="false">N26*(1-O26)</f>
-        <v>777.98</v>
+        <v>311.08</v>
       </c>
       <c r="R26" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="26" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="B27" s="30" t="n">
         <v>1</v>
@@ -10561,39 +10747,39 @@
         <v>0</v>
       </c>
       <c r="K27" s="40" t="n">
-        <f aca="false">H27*(J27*manut_dia+(C27-J27)*manut_med)</f>
-        <v>411.4</v>
+        <f aca="false">H27*(J27*manut_dia_copr+(C27-J27)*manut_med_copr)</f>
+        <v>330</v>
       </c>
       <c r="L27" s="40" t="n">
-        <f aca="false">I27*J27*alojamiento</f>
+        <f aca="false">I27*J27*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M27" s="40" t="n">
-        <f aca="false">C27*bus_dia*CEILING(I27/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C27*MIN(CEILING(I27/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>114.4</v>
       </c>
       <c r="N27" s="41" t="n">
         <f aca="false">K27+L27+M27</f>
-        <v>1111.4</v>
+        <v>444.4</v>
       </c>
       <c r="O27" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="P27" s="40" t="n">
         <f aca="false">N27*O27</f>
-        <v>333.42</v>
+        <v>133.32</v>
       </c>
       <c r="Q27" s="40" t="n">
         <f aca="false">N27*(1-O27)</f>
-        <v>777.98</v>
+        <v>311.08</v>
       </c>
       <c r="R27" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="26" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B28" s="30" t="n">
         <v>1</v>
@@ -10628,39 +10814,39 @@
         <v>0</v>
       </c>
       <c r="K28" s="40" t="n">
-        <f aca="false">H28*(J28*manut_dia+(C28-J28)*manut_med)</f>
-        <v>411.4</v>
+        <f aca="false">H28*(J28*manut_dia_copr+(C28-J28)*manut_med_copr)</f>
+        <v>330</v>
       </c>
       <c r="L28" s="40" t="n">
-        <f aca="false">I28*J28*alojamiento</f>
+        <f aca="false">I28*J28*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M28" s="40" t="n">
-        <f aca="false">C28*bus_dia*CEILING(I28/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C28*MIN(CEILING(I28/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>114.4</v>
       </c>
       <c r="N28" s="41" t="n">
         <f aca="false">K28+L28+M28</f>
-        <v>1111.4</v>
+        <v>444.4</v>
       </c>
       <c r="O28" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="P28" s="40" t="n">
         <f aca="false">N28*O28</f>
-        <v>333.42</v>
+        <v>133.32</v>
       </c>
       <c r="Q28" s="40" t="n">
         <f aca="false">N28*(1-O28)</f>
-        <v>777.98</v>
+        <v>311.08</v>
       </c>
       <c r="R28" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="B29" s="30" t="n">
         <v>1</v>
@@ -10695,39 +10881,39 @@
         <v>0</v>
       </c>
       <c r="K29" s="40" t="n">
-        <f aca="false">H29*(J29*manut_dia+(C29-J29)*manut_med)</f>
-        <v>411.4</v>
+        <f aca="false">H29*(J29*manut_dia_copr+(C29-J29)*manut_med_copr)</f>
+        <v>330</v>
       </c>
       <c r="L29" s="40" t="n">
-        <f aca="false">I29*J29*alojamiento</f>
+        <f aca="false">I29*J29*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M29" s="40" t="n">
-        <f aca="false">C29*bus_dia*CEILING(I29/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C29*MIN(CEILING(I29/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>114.4</v>
       </c>
       <c r="N29" s="41" t="n">
         <f aca="false">K29+L29+M29</f>
-        <v>1111.4</v>
+        <v>444.4</v>
       </c>
       <c r="O29" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="P29" s="40" t="n">
         <f aca="false">N29*O29</f>
-        <v>333.42</v>
+        <v>133.32</v>
       </c>
       <c r="Q29" s="40" t="n">
         <f aca="false">N29*(1-O29)</f>
-        <v>777.98</v>
+        <v>311.08</v>
       </c>
       <c r="R29" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="26" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="B30" s="30" t="n">
         <v>1</v>
@@ -10762,39 +10948,39 @@
         <v>0</v>
       </c>
       <c r="K30" s="40" t="n">
-        <f aca="false">H30*(J30*manut_dia+(C30-J30)*manut_med)</f>
-        <v>822.8</v>
+        <f aca="false">H30*(J30*manut_dia_copr+(C30-J30)*manut_med_copr)</f>
+        <v>660</v>
       </c>
       <c r="L30" s="40" t="n">
-        <f aca="false">I30*J30*alojamiento</f>
+        <f aca="false">I30*J30*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M30" s="40" t="n">
-        <f aca="false">C30*bus_dia*CEILING(I30/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C30*MIN(CEILING(I30/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>171.6</v>
       </c>
       <c r="N30" s="41" t="n">
         <f aca="false">K30+L30+M30</f>
-        <v>1522.8</v>
+        <v>831.6</v>
       </c>
       <c r="O30" s="48" t="n">
         <v>0.5</v>
       </c>
       <c r="P30" s="40" t="n">
         <f aca="false">N30*O30</f>
-        <v>761.4</v>
+        <v>415.8</v>
       </c>
       <c r="Q30" s="40" t="n">
         <f aca="false">N30*(1-O30)</f>
-        <v>761.4</v>
+        <v>415.8</v>
       </c>
       <c r="R30" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="26" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="B31" s="30" t="n">
         <v>1</v>
@@ -10829,39 +11015,39 @@
         <v>0</v>
       </c>
       <c r="K31" s="40" t="n">
-        <f aca="false">H31*(J31*manut_dia+(C31-J31)*manut_med)</f>
-        <v>374</v>
+        <f aca="false">H31*(J31*manut_dia_copr+(C31-J31)*manut_med_copr)</f>
+        <v>300</v>
       </c>
       <c r="L31" s="40" t="n">
-        <f aca="false">I31*J31*alojamiento</f>
+        <f aca="false">I31*J31*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M31" s="40" t="n">
-        <f aca="false">C31*bus_dia*CEILING(I31/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C31*MIN(CEILING(I31/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>57.2</v>
       </c>
       <c r="N31" s="41" t="n">
         <f aca="false">K31+L31+M31</f>
-        <v>1074</v>
+        <v>357.2</v>
       </c>
       <c r="O31" s="48" t="n">
         <v>0.85</v>
       </c>
       <c r="P31" s="40" t="n">
         <f aca="false">N31*O31</f>
-        <v>912.9</v>
+        <v>303.62</v>
       </c>
       <c r="Q31" s="40" t="n">
         <f aca="false">N31*(1-O31)</f>
-        <v>161.1</v>
+        <v>53.58</v>
       </c>
       <c r="R31" s="28" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="26" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="B32" s="30" t="n">
         <v>1</v>
@@ -10896,40 +11082,40 @@
         <v>0</v>
       </c>
       <c r="K32" s="40" t="n">
-        <f aca="false">H32*(J32*manut_dia+(C32-J32)*manut_med)</f>
-        <v>374</v>
+        <f aca="false">H32*(J32*manut_dia_copr+(C32-J32)*manut_med_copr)</f>
+        <v>300</v>
       </c>
       <c r="L32" s="40" t="n">
-        <f aca="false">I32*J32*alojamiento</f>
+        <f aca="false">I32*J32*alojamiento_copr</f>
         <v>0</v>
       </c>
       <c r="M32" s="40" t="n">
-        <f aca="false">C32*bus_dia*CEILING(I32/cap_bus,1)</f>
-        <v>700</v>
+        <f aca="false">C32*MIN(CEILING(I32/cap_vehiculo_copr,1),n_vehiculos_copr)*km_madrid_pastrana*2*km_coche</f>
+        <v>57.2</v>
       </c>
       <c r="N32" s="41" t="n">
         <f aca="false">K32+L32+M32</f>
-        <v>1074</v>
+        <v>357.2</v>
       </c>
       <c r="O32" s="48" t="n">
         <v>0.85</v>
       </c>
       <c r="P32" s="40" t="n">
         <f aca="false">N32*O32</f>
-        <v>912.9</v>
+        <v>303.62</v>
       </c>
       <c r="Q32" s="40" t="n">
         <f aca="false">N32*(1-O32)</f>
-        <v>161.1</v>
+        <v>53.58</v>
       </c>
       <c r="R32" s="28" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="31"/>
       <c r="B33" s="32" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="C33" s="31"/>
       <c r="D33" s="42" t="n">
@@ -10953,35 +11139,35 @@
       <c r="J33" s="31"/>
       <c r="K33" s="43" t="n">
         <f aca="false">SUM(K5:K32)</f>
-        <v>18400.8</v>
+        <v>14760</v>
       </c>
       <c r="L33" s="43" t="n">
         <f aca="false">SUM(L5:L32)</f>
-        <v>11082.96</v>
+        <v>9240</v>
       </c>
       <c r="M33" s="43" t="n">
         <f aca="false">SUM(M5:M32)</f>
-        <v>25200</v>
+        <v>3489.2</v>
       </c>
       <c r="N33" s="43" t="n">
         <f aca="false">SUM(N5:N32)</f>
-        <v>54683.76</v>
+        <v>27489.2</v>
       </c>
       <c r="O33" s="31"/>
       <c r="P33" s="43" t="n">
         <f aca="false">SUM(P5:P32)</f>
-        <v>30874.23</v>
+        <v>15661</v>
       </c>
       <c r="Q33" s="43" t="n">
         <f aca="false">SUM(Q5:Q32)</f>
-        <v>23809.53</v>
+        <v>11828.2</v>
       </c>
       <c r="R33" s="31"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="31"/>
       <c r="B34" s="32" t="s">
-        <v>547</v>
+        <v>561</v>
       </c>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
@@ -10996,7 +11182,7 @@
       <c r="M34" s="31"/>
       <c r="N34" s="43" t="n">
         <f aca="false">SUMIFS(N5:N32,R5:R32,"P1")</f>
-        <v>17540.91</v>
+        <v>8997.4</v>
       </c>
       <c r="O34" s="31"/>
       <c r="P34" s="31"/>
@@ -11006,7 +11192,7 @@
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="31"/>
       <c r="B35" s="32" t="s">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="C35" s="31"/>
       <c r="D35" s="31"/>
@@ -11021,7 +11207,7 @@
       <c r="M35" s="31"/>
       <c r="N35" s="43" t="n">
         <f aca="false">SUMIFS(N5:N32,R5:R32,"P2")</f>
-        <v>37142.85</v>
+        <v>18491.8</v>
       </c>
       <c r="O35" s="31"/>
       <c r="P35" s="31"/>
@@ -11064,7 +11250,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -11078,7 +11264,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11092,42 +11278,42 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>48</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>552</v>
+        <v>566</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>554</v>
+        <v>568</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>555</v>
+        <v>569</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="C5" s="28" t="n">
         <v>1</v>
@@ -11155,15 +11341,15 @@
         <v>500</v>
       </c>
       <c r="J5" s="28" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>558</v>
+        <v>572</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>559</v>
+        <v>573</v>
       </c>
       <c r="C6" s="28" t="n">
         <v>24</v>
@@ -11189,15 +11375,15 @@
         <v>336</v>
       </c>
       <c r="J6" s="28" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>558</v>
+        <v>572</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="C7" s="28" t="n">
         <v>36</v>
@@ -11223,15 +11409,15 @@
         <v>504</v>
       </c>
       <c r="J7" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="C8" s="28" t="n">
         <v>1</v>
@@ -11257,15 +11443,15 @@
         <v>200</v>
       </c>
       <c r="J8" s="28" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>563</v>
+        <v>577</v>
       </c>
       <c r="C9" s="28" t="n">
         <v>1</v>
@@ -11291,15 +11477,15 @@
         <v>300</v>
       </c>
       <c r="J9" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>565</v>
+        <v>579</v>
       </c>
       <c r="C10" s="28" t="n">
         <v>1</v>
@@ -11327,15 +11513,15 @@
         <v>1400</v>
       </c>
       <c r="J10" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="C11" s="28" t="n">
         <v>1</v>
@@ -11361,15 +11547,15 @@
         <v>750</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="C12" s="28" t="n">
         <v>1</v>
@@ -11395,15 +11581,15 @@
         <v>1750</v>
       </c>
       <c r="J12" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="C13" s="28" t="n">
         <v>1</v>
@@ -11429,15 +11615,15 @@
         <v>250</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>571</v>
+        <v>585</v>
       </c>
       <c r="C14" s="28" t="n">
         <v>1</v>
@@ -11463,13 +11649,13 @@
         <v>500</v>
       </c>
       <c r="J14" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31"/>
       <c r="B15" s="32" t="s">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="C15" s="31"/>
       <c r="D15" s="31"/>
@@ -11506,7 +11692,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -11519,7 +11705,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>573</v>
+        <v>587</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -11534,7 +11720,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -11552,31 +11738,31 @@
         <v>48</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>576</v>
+        <v>590</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>545</v>
+        <v>559</v>
       </c>
       <c r="K4" s="12" t="s">
         <v>52</v>
@@ -11584,464 +11770,468 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>581</v>
+        <v>595</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="C5" s="49" t="n">
-        <v>8000</v>
+        <v>3500</v>
       </c>
       <c r="D5" s="28" t="n">
         <v>60</v>
       </c>
       <c r="E5" s="40" t="n">
         <f aca="false">C5/D5*meses_p1</f>
-        <v>933.333333333333</v>
+        <v>408.333333333333</v>
       </c>
       <c r="F5" s="40" t="n">
         <f aca="false">C5/D5*meses_p2</f>
-        <v>1333.33333333333</v>
+        <v>583.333333333333</v>
       </c>
       <c r="G5" s="41" t="n">
         <f aca="false">E5+F5</f>
-        <v>2266.66666666667</v>
+        <v>991.666666666667</v>
       </c>
       <c r="H5" s="48" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="40" t="n">
         <f aca="false">G5*H5</f>
-        <v>2266.66666666667</v>
+        <v>991.666666666667</v>
       </c>
       <c r="J5" s="40" t="n">
         <f aca="false">G5*(1-H5)</f>
         <v>0</v>
       </c>
       <c r="K5" s="51" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>584</v>
+        <v>598</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>585</v>
+        <v>599</v>
       </c>
       <c r="C6" s="49" t="n">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="D6" s="28" t="n">
         <v>60</v>
       </c>
       <c r="E6" s="40" t="n">
         <f aca="false">C6/D6*meses_p1</f>
-        <v>583.333333333333</v>
+        <v>525</v>
       </c>
       <c r="F6" s="40" t="n">
         <f aca="false">C6/D6*meses_p2</f>
-        <v>833.333333333333</v>
+        <v>750</v>
       </c>
       <c r="G6" s="41" t="n">
         <f aca="false">E6+F6</f>
-        <v>1416.66666666667</v>
+        <v>1275</v>
       </c>
       <c r="H6" s="48" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="40" t="n">
         <f aca="false">G6*H6</f>
-        <v>1416.66666666667</v>
+        <v>1275</v>
       </c>
       <c r="J6" s="40" t="n">
         <f aca="false">G6*(1-H6)</f>
         <v>0</v>
       </c>
       <c r="K6" s="51" t="s">
-        <v>586</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>587</v>
+        <v>601</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="C7" s="49" t="n">
-        <v>3000</v>
+        <v>3700</v>
       </c>
       <c r="D7" s="28" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="E7" s="40" t="n">
         <f aca="false">C7/D7*meses_p1</f>
-        <v>1235.29411764706</v>
+        <v>431.666666666667</v>
       </c>
       <c r="F7" s="40" t="n">
         <f aca="false">C7/D7*meses_p2</f>
-        <v>1764.70588235294</v>
+        <v>616.666666666667</v>
       </c>
       <c r="G7" s="41" t="n">
         <f aca="false">E7+F7</f>
-        <v>3000</v>
+        <v>1048.33333333333</v>
       </c>
       <c r="H7" s="48" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="40" t="n">
         <f aca="false">G7*H7</f>
-        <v>3000</v>
+        <v>1048.33333333333</v>
       </c>
       <c r="J7" s="40" t="n">
         <f aca="false">G7*(1-H7)</f>
         <v>0</v>
       </c>
       <c r="K7" s="51" t="s">
-        <v>589</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>590</v>
+        <v>604</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>591</v>
+        <v>605</v>
       </c>
       <c r="C8" s="49" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="D8" s="28" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="E8" s="40" t="n">
         <f aca="false">C8/D8*meses_p1</f>
-        <v>233.333333333333</v>
+        <v>1235.29411764706</v>
       </c>
       <c r="F8" s="40" t="n">
         <f aca="false">C8/D8*meses_p2</f>
-        <v>333.333333333333</v>
+        <v>1764.70588235294</v>
       </c>
       <c r="G8" s="41" t="n">
         <f aca="false">E8+F8</f>
-        <v>566.666666666667</v>
+        <v>3000</v>
       </c>
       <c r="H8" s="48" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="40" t="n">
         <f aca="false">G8*H8</f>
-        <v>566.666666666667</v>
+        <v>3000</v>
       </c>
       <c r="J8" s="40" t="n">
         <f aca="false">G8*(1-H8)</f>
         <v>0</v>
       </c>
       <c r="K8" s="51" t="s">
-        <v>592</v>
+        <v>606</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="31"/>
-      <c r="B9" s="32" t="s">
-        <v>593</v>
-      </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="43" t="n">
-        <f aca="false">SUM(E5:E8)</f>
-        <v>2985.29411764706</v>
-      </c>
-      <c r="F9" s="43" t="n">
-        <f aca="false">SUM(F5:F8)</f>
-        <v>4264.70588235294</v>
-      </c>
-      <c r="G9" s="43" t="n">
-        <f aca="false">SUM(G5:G8)</f>
-        <v>7250</v>
-      </c>
-      <c r="H9" s="31"/>
-      <c r="I9" s="43" t="n">
-        <f aca="false">SUM(I5:I8)</f>
-        <v>7250</v>
-      </c>
-      <c r="J9" s="43" t="n">
-        <f aca="false">SUM(J5:J8)</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="31"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
+      <c r="A9" s="26" t="s">
+        <v>607</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>608</v>
+      </c>
+      <c r="C9" s="49" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="E9" s="40" t="n">
+        <f aca="false">C9/D9*meses_p1</f>
+        <v>233.333333333333</v>
+      </c>
+      <c r="F9" s="40" t="n">
+        <f aca="false">C9/D9*meses_p2</f>
+        <v>333.333333333333</v>
+      </c>
+      <c r="G9" s="41" t="n">
+        <f aca="false">E9+F9</f>
+        <v>566.666666666667</v>
+      </c>
+      <c r="H9" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="40" t="n">
+        <f aca="false">G9*H9</f>
+        <v>566.666666666667</v>
+      </c>
+      <c r="J9" s="40" t="n">
+        <f aca="false">G9*(1-H9)</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="31"/>
+      <c r="B10" s="32" t="s">
+        <v>610</v>
+      </c>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="43" t="n">
+        <f aca="false">SUM(E5:E9)</f>
+        <v>2833.62745098039</v>
+      </c>
+      <c r="F10" s="43" t="n">
+        <f aca="false">SUM(F5:F9)</f>
+        <v>4048.03921568627</v>
+      </c>
+      <c r="G10" s="43" t="n">
+        <f aca="false">SUM(G5:G9)</f>
+        <v>6881.66666666667</v>
+      </c>
+      <c r="H10" s="31"/>
+      <c r="I10" s="43" t="n">
+        <f aca="false">SUM(I5:I9)</f>
+        <v>6881.66666666667</v>
+      </c>
+      <c r="J10" s="43" t="n">
+        <f aca="false">SUM(J5:J9)</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="31"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>575</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>552</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>553</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>494</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>543</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>544</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>545</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>595</v>
-      </c>
-      <c r="K13" s="12"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="26" t="s">
-        <v>596</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>597</v>
-      </c>
-      <c r="C14" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="49" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E14" s="41" t="n">
-        <f aca="false">C14*D14</f>
-        <v>2500</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>347</v>
-      </c>
-      <c r="G14" s="48" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H14" s="40" t="n">
-        <f aca="false">E14*G14</f>
-        <v>750</v>
-      </c>
-      <c r="I14" s="40" t="n">
-        <f aca="false">E14*(1-G14)</f>
-        <v>1750</v>
-      </c>
-      <c r="J14" s="30" t="s">
-        <v>598</v>
-      </c>
-      <c r="K14" s="27"/>
+      <c r="B14" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>566</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="K14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="C15" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="49" t="n">
-        <v>13500</v>
+        <v>2500</v>
       </c>
       <c r="E15" s="41" t="n">
         <f aca="false">C15*D15</f>
-        <v>13500</v>
+        <v>2500</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="G15" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="H15" s="40" t="n">
         <f aca="false">E15*G15</f>
-        <v>4050</v>
+        <v>750</v>
       </c>
       <c r="I15" s="40" t="n">
         <f aca="false">E15*(1-G15)</f>
-        <v>9450</v>
+        <v>1750</v>
       </c>
       <c r="J15" s="30" t="s">
-        <v>598</v>
+        <v>615</v>
       </c>
       <c r="K15" s="27"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>601</v>
+        <v>616</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>602</v>
+        <v>617</v>
       </c>
       <c r="C16" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="49" t="n">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="E16" s="41" t="n">
         <f aca="false">C16*D16</f>
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="G16" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="H16" s="40" t="n">
         <f aca="false">E16*G16</f>
-        <v>1200</v>
+        <v>1050</v>
       </c>
       <c r="I16" s="40" t="n">
         <f aca="false">E16*(1-G16)</f>
-        <v>2800</v>
+        <v>2450</v>
       </c>
       <c r="J16" s="30" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="K16" s="27"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>603</v>
+        <v>618</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
       <c r="C17" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="49" t="n">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="E17" s="41" t="n">
         <f aca="false">C17*D17</f>
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="G17" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="H17" s="40" t="n">
         <f aca="false">E17*G17</f>
-        <v>1050</v>
+        <v>450</v>
       </c>
       <c r="I17" s="40" t="n">
         <f aca="false">E17*(1-G17)</f>
-        <v>2450</v>
+        <v>1050</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>370</v>
+        <v>615</v>
       </c>
       <c r="K17" s="27"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>605</v>
+        <v>620</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
       <c r="C18" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="49" t="n">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="E18" s="41" t="n">
         <f aca="false">C18*D18</f>
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="G18" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="H18" s="40" t="n">
         <f aca="false">E18*G18</f>
-        <v>750</v>
+        <v>1350</v>
       </c>
       <c r="I18" s="40" t="n">
         <f aca="false">E18*(1-G18)</f>
-        <v>1750</v>
+        <v>3150</v>
       </c>
       <c r="J18" s="30" t="s">
-        <v>607</v>
+        <v>381</v>
       </c>
       <c r="K18" s="27"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>609</v>
+        <v>623</v>
       </c>
       <c r="C19" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="49" t="n">
-        <v>8000</v>
+        <v>3000</v>
       </c>
       <c r="E19" s="41" t="n">
         <f aca="false">C19*D19</f>
-        <v>8000</v>
+        <v>3000</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="G19" s="48" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H19" s="40" t="n">
         <f aca="false">E19*G19</f>
-        <v>4800</v>
+        <v>900</v>
       </c>
       <c r="I19" s="40" t="n">
         <f aca="false">E19*(1-G19)</f>
-        <v>3200</v>
+        <v>2100</v>
       </c>
       <c r="J19" s="30" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="K19" s="27"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>610</v>
+        <v>624</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>611</v>
+        <v>625</v>
       </c>
       <c r="C20" s="28" t="n">
         <v>1</v>
@@ -12054,161 +12244,305 @@
         <v>2500</v>
       </c>
       <c r="F20" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="G20" s="48" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H20" s="40" t="n">
         <f aca="false">E20*G20</f>
-        <v>1250</v>
+        <v>750</v>
       </c>
       <c r="I20" s="40" t="n">
         <f aca="false">E20*(1-G20)</f>
-        <v>1250</v>
+        <v>1750</v>
       </c>
       <c r="J20" s="30" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="K20" s="27"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>613</v>
+        <v>627</v>
       </c>
       <c r="C21" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="49" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E21" s="41" t="n">
         <f aca="false">C21*D21</f>
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H21" s="40" t="n">
         <f aca="false">E21*G21</f>
-        <v>400</v>
+        <v>750</v>
       </c>
       <c r="I21" s="40" t="n">
         <f aca="false">E21*(1-G21)</f>
-        <v>1600</v>
+        <v>1750</v>
       </c>
       <c r="J21" s="30" t="s">
-        <v>614</v>
+        <v>628</v>
       </c>
       <c r="K21" s="27"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>615</v>
+        <v>629</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>616</v>
+        <v>630</v>
       </c>
       <c r="C22" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="49" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="E22" s="41" t="n">
         <f aca="false">C22*D22</f>
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="G22" s="48" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H22" s="40" t="n">
         <f aca="false">E22*G22</f>
-        <v>1050</v>
+        <v>2700</v>
       </c>
       <c r="I22" s="40" t="n">
         <f aca="false">E22*(1-G22)</f>
-        <v>450</v>
+        <v>1800</v>
       </c>
       <c r="J22" s="30" t="s">
-        <v>617</v>
+        <v>387</v>
       </c>
       <c r="K22" s="27"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>618</v>
+        <v>631</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>619</v>
+        <v>632</v>
       </c>
       <c r="C23" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="49" t="n">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="E23" s="41" t="n">
         <f aca="false">C23*D23</f>
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="G23" s="48" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H23" s="40" t="n">
         <f aca="false">E23*G23</f>
-        <v>800</v>
+        <v>2100</v>
       </c>
       <c r="I23" s="40" t="n">
         <f aca="false">E23*(1-G23)</f>
+        <v>1400</v>
+      </c>
+      <c r="J23" s="30" t="s">
+        <v>387</v>
+      </c>
+      <c r="K23" s="27"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="26" t="s">
+        <v>633</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>634</v>
+      </c>
+      <c r="C24" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="49" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E24" s="41" t="n">
+        <f aca="false">C24*D24</f>
+        <v>2500</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="G24" s="48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H24" s="40" t="n">
+        <f aca="false">E24*G24</f>
+        <v>1250</v>
+      </c>
+      <c r="I24" s="40" t="n">
+        <f aca="false">E24*(1-G24)</f>
+        <v>1250</v>
+      </c>
+      <c r="J24" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="K24" s="27"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="26" t="s">
+        <v>635</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>636</v>
+      </c>
+      <c r="C25" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="49" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E25" s="41" t="n">
+        <f aca="false">C25*D25</f>
+        <v>2000</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="G25" s="48" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H25" s="40" t="n">
+        <f aca="false">E25*G25</f>
+        <v>400</v>
+      </c>
+      <c r="I25" s="40" t="n">
+        <f aca="false">E25*(1-G25)</f>
+        <v>1600</v>
+      </c>
+      <c r="J25" s="30" t="s">
+        <v>637</v>
+      </c>
+      <c r="K25" s="27"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="26" t="s">
+        <v>638</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>639</v>
+      </c>
+      <c r="C26" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="49" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E26" s="41" t="n">
+        <f aca="false">C26*D26</f>
+        <v>1500</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="G26" s="48" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H26" s="40" t="n">
+        <f aca="false">E26*G26</f>
+        <v>1050</v>
+      </c>
+      <c r="I26" s="40" t="n">
+        <f aca="false">E26*(1-G26)</f>
+        <v>450</v>
+      </c>
+      <c r="J26" s="30" t="s">
+        <v>640</v>
+      </c>
+      <c r="K26" s="27"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="26" t="s">
+        <v>641</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>642</v>
+      </c>
+      <c r="C27" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="49" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E27" s="41" t="n">
+        <f aca="false">C27*D27</f>
+        <v>2000</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="G27" s="48" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H27" s="40" t="n">
+        <f aca="false">E27*G27</f>
+        <v>800</v>
+      </c>
+      <c r="I27" s="40" t="n">
+        <f aca="false">E27*(1-G27)</f>
         <v>1200</v>
       </c>
-      <c r="J23" s="30" t="s">
-        <v>617</v>
-      </c>
-      <c r="K23" s="27"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="31"/>
-      <c r="B24" s="32" t="s">
-        <v>620</v>
-      </c>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="43" t="n">
-        <f aca="false">SUM(E14:E23)</f>
-        <v>42000</v>
-      </c>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="43" t="n">
-        <f aca="false">SUM(H14:H23)</f>
-        <v>16100</v>
-      </c>
-      <c r="I24" s="43" t="n">
-        <f aca="false">SUM(I14:I23)</f>
-        <v>25900</v>
-      </c>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
+      <c r="J27" s="30" t="s">
+        <v>640</v>
+      </c>
+      <c r="K27" s="27"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="31"/>
+      <c r="B28" s="32" t="s">
+        <v>643</v>
+      </c>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="43" t="n">
+        <f aca="false">SUM(E15:E27)</f>
+        <v>36000</v>
+      </c>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="43" t="n">
+        <f aca="false">SUM(H15:H27)</f>
+        <v>14300</v>
+      </c>
+      <c r="I28" s="43" t="n">
+        <f aca="false">SUM(I15:I27)</f>
+        <v>21700</v>
+      </c>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A13:K13"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -12235,7 +12569,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>621</v>
+        <v>644</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -12249,7 +12583,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>622</v>
+        <v>645</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -12263,7 +12597,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>623</v>
+        <v>646</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -12277,30 +12611,30 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>624</v>
+        <v>647</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>625</v>
+        <v>648</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>626</v>
+        <v>649</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>627</v>
+        <v>650</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>628</v>
+        <v>651</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B6" s="39" t="str">
         <f aca="false">VLOOKUP(A6,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -12329,7 +12663,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B7" s="39" t="str">
         <f aca="false">VLOOKUP(A7,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -12358,7 +12692,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="B8" s="39" t="str">
         <f aca="false">VLOOKUP(A8,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -12387,7 +12721,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B9" s="39" t="str">
         <f aca="false">VLOOKUP(A9,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -12416,7 +12750,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B10" s="39" t="str">
         <f aca="false">VLOOKUP(A10,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -12445,7 +12779,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B11" s="39" t="str">
         <f aca="false">VLOOKUP(A11,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -12474,7 +12808,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="B12" s="39" t="str">
         <f aca="false">VLOOKUP(A12,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -12503,7 +12837,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="B13" s="39" t="str">
         <f aca="false">VLOOKUP(A13,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -12533,7 +12867,7 @@
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="31"/>
       <c r="B14" s="32" t="s">
-        <v>629</v>
+        <v>652</v>
       </c>
       <c r="C14" s="43" t="n">
         <f aca="false">SUM(C6:C13)</f>
@@ -12558,7 +12892,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="52" t="s">
-        <v>630</v>
+        <v>653</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12566,15 +12900,15 @@
         <v>48</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>631</v>
+        <v>654</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>632</v>
+        <v>655</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="27" t="s">
-        <v>633</v>
+        <v>656</v>
       </c>
       <c r="C18" s="50" t="n">
         <f aca="false">PERSONAL!$H$82+PERSONAL!$H$84</f>
@@ -12584,17 +12918,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="27" t="s">
-        <v>634</v>
+        <v>657</v>
       </c>
       <c r="C19" s="50" t="n">
         <f aca="false">VIAJES!$N$34</f>
-        <v>17540.91</v>
+        <v>8997.4</v>
       </c>
       <c r="D19" s="27"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="27" t="s">
-        <v>635</v>
+        <v>658</v>
       </c>
       <c r="C20" s="50" t="n">
         <f aca="false">SUMIFS(MATERIALES!$E$5:$E$14,MATERIALES!$A$5:$A$14,"B.2",MATERIALES!$J$5:$J$14,"P1")</f>
@@ -12604,7 +12938,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="27" t="s">
-        <v>636</v>
+        <v>659</v>
       </c>
       <c r="C21" s="50" t="n">
         <f aca="false">SUMIFS(MATERIALES!$E$5:$E$14,MATERIALES!$A$5:$A$14,"B.3",MATERIALES!$J$5:$J$14,"P1")</f>
@@ -12614,7 +12948,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="27" t="s">
-        <v>637</v>
+        <v>660</v>
       </c>
       <c r="C22" s="50" t="n">
         <f aca="false">SUMIFS(MATERIALES!$E$5:$E$14,MATERIALES!$A$5:$A$14,"B.4",MATERIALES!$J$5:$J$14,"P1")</f>
@@ -12624,7 +12958,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="27" t="s">
-        <v>638</v>
+        <v>661</v>
       </c>
       <c r="C23" s="50" t="n">
         <f aca="false">SUMIFS(MATERIALES!$E$5:$E$14,MATERIALES!$A$5:$A$14,"B.5",MATERIALES!$J$5:$J$14,"P1")</f>
@@ -12634,7 +12968,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="27" t="s">
-        <v>639</v>
+        <v>662</v>
       </c>
       <c r="C24" s="50" t="n">
         <f aca="false">SUMIFS(MATERIALES!$E$5:$E$14,MATERIALES!$A$5:$A$14,"B.6",MATERIALES!$J$5:$J$14,"P1")</f>
@@ -12644,7 +12978,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="27" t="s">
-        <v>640</v>
+        <v>663</v>
       </c>
       <c r="C25" s="50" t="n">
         <f aca="false">SUMIFS(MATERIALES!$E$5:$E$14,MATERIALES!$A$5:$A$14,"B.7",MATERIALES!$J$5:$J$14,"P1")</f>
@@ -12654,27 +12988,27 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="27" t="s">
-        <v>641</v>
+        <v>664</v>
       </c>
       <c r="C26" s="50" t="n">
-        <f aca="false">INVERSIONES!$E$9</f>
-        <v>2985.29411764706</v>
+        <f aca="false">INVERSIONES!$E$10</f>
+        <v>2833.62745098039</v>
       </c>
       <c r="D26" s="27"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="27" t="s">
-        <v>642</v>
+        <v>665</v>
       </c>
       <c r="C27" s="50" t="n">
-        <f aca="false">SUMIFS(INVERSIONES!$E$14:$E$23,INVERSIONES!$F$14:$F$23,"P1")</f>
+        <f aca="false">SUMIFS(INVERSIONES!$E$15:$E$27,INVERSIONES!$F$15:$F$27,"P1")</f>
         <v>0</v>
       </c>
       <c r="D27" s="27"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="26" t="s">
-        <v>643</v>
+        <v>666</v>
       </c>
       <c r="C28" s="41" t="n">
         <f aca="false">($G$14+C18)*tasa_ind</f>
@@ -12684,27 +13018,27 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="32" t="s">
-        <v>644</v>
+        <v>667</v>
       </c>
       <c r="C29" s="43" t="n">
         <f aca="false">SUM(C18:C28)</f>
-        <v>43499.2861176471</v>
+        <v>34804.1094509804</v>
       </c>
       <c r="D29" s="31"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="53" t="s">
-        <v>645</v>
+        <v>668</v>
       </c>
       <c r="C30" s="54" t="n">
         <f aca="false">$G$14+$C$29</f>
-        <v>72284.5261176471</v>
+        <v>63589.3494509804</v>
       </c>
       <c r="D30" s="55"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>646</v>
+        <v>669</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -12718,30 +13052,30 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>624</v>
+        <v>647</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>625</v>
+        <v>648</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>626</v>
+        <v>649</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>627</v>
+        <v>650</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>628</v>
+        <v>651</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="26" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="B34" s="39" t="str">
         <f aca="false">VLOOKUP(A34,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -12770,7 +13104,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="26" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="B35" s="39" t="str">
         <f aca="false">VLOOKUP(A35,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -12799,7 +13133,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="26" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B36" s="39" t="str">
         <f aca="false">VLOOKUP(A36,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -12828,7 +13162,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="26" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B37" s="39" t="str">
         <f aca="false">VLOOKUP(A37,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -12857,7 +13191,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="26" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B38" s="39" t="str">
         <f aca="false">VLOOKUP(A38,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -12886,7 +13220,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="26" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="B39" s="39" t="str">
         <f aca="false">VLOOKUP(A39,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -12915,7 +13249,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="26" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="B40" s="39" t="str">
         <f aca="false">VLOOKUP(A40,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -12944,7 +13278,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="26" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B41" s="39" t="str">
         <f aca="false">VLOOKUP(A41,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -12973,7 +13307,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="26" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="B42" s="39" t="str">
         <f aca="false">VLOOKUP(A42,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -13002,7 +13336,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="26" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="B43" s="39" t="str">
         <f aca="false">VLOOKUP(A43,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -13031,7 +13365,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="26" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="B44" s="39" t="str">
         <f aca="false">VLOOKUP(A44,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -13060,7 +13394,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="26" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="B45" s="39" t="str">
         <f aca="false">VLOOKUP(A45,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -13089,7 +13423,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="26" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="B46" s="39" t="str">
         <f aca="false">VLOOKUP(A46,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -13118,7 +13452,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="26" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="B47" s="39" t="str">
         <f aca="false">VLOOKUP(A47,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -13147,7 +13481,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="26" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B48" s="39" t="str">
         <f aca="false">VLOOKUP(A48,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -13176,7 +13510,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="26" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="B49" s="39" t="str">
         <f aca="false">VLOOKUP(A49,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -13205,7 +13539,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="26" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="B50" s="39" t="str">
         <f aca="false">VLOOKUP(A50,ACTIVIDADES!$A$5:$C$50,3,FALSE())</f>
@@ -13235,7 +13569,7 @@
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="31"/>
       <c r="B51" s="32" t="s">
-        <v>629</v>
+        <v>652</v>
       </c>
       <c r="C51" s="43" t="n">
         <f aca="false">SUM(C34:C50)</f>
@@ -13260,7 +13594,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="52" t="s">
-        <v>647</v>
+        <v>670</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13268,15 +13602,15 @@
         <v>48</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>631</v>
+        <v>654</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>632</v>
+        <v>655</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="27" t="s">
-        <v>633</v>
+        <v>656</v>
       </c>
       <c r="C55" s="50" t="n">
         <f aca="false">PERSONAL!$H$83+PERSONAL!$H$85</f>
@@ -13286,17 +13620,17 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="27" t="s">
-        <v>634</v>
+        <v>657</v>
       </c>
       <c r="C56" s="50" t="n">
         <f aca="false">VIAJES!$N$35</f>
-        <v>37142.85</v>
+        <v>18491.8</v>
       </c>
       <c r="D56" s="27"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="27" t="s">
-        <v>635</v>
+        <v>658</v>
       </c>
       <c r="C57" s="50" t="n">
         <f aca="false">SUMIFS(MATERIALES!$E$5:$E$14,MATERIALES!$A$5:$A$14,"B.2",MATERIALES!$J$5:$J$14,"P2")</f>
@@ -13306,7 +13640,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="27" t="s">
-        <v>636</v>
+        <v>659</v>
       </c>
       <c r="C58" s="50" t="n">
         <f aca="false">SUMIFS(MATERIALES!$E$5:$E$14,MATERIALES!$A$5:$A$14,"B.3",MATERIALES!$J$5:$J$14,"P2")</f>
@@ -13316,7 +13650,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="27" t="s">
-        <v>637</v>
+        <v>660</v>
       </c>
       <c r="C59" s="50" t="n">
         <f aca="false">SUMIFS(MATERIALES!$E$5:$E$14,MATERIALES!$A$5:$A$14,"B.4",MATERIALES!$J$5:$J$14,"P2")</f>
@@ -13326,7 +13660,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="27" t="s">
-        <v>638</v>
+        <v>661</v>
       </c>
       <c r="C60" s="50" t="n">
         <f aca="false">SUMIFS(MATERIALES!$E$5:$E$14,MATERIALES!$A$5:$A$14,"B.5",MATERIALES!$J$5:$J$14,"P2")</f>
@@ -13336,7 +13670,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="27" t="s">
-        <v>639</v>
+        <v>662</v>
       </c>
       <c r="C61" s="50" t="n">
         <f aca="false">SUMIFS(MATERIALES!$E$5:$E$14,MATERIALES!$A$5:$A$14,"B.6",MATERIALES!$J$5:$J$14,"P2")</f>
@@ -13346,7 +13680,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="27" t="s">
-        <v>640</v>
+        <v>663</v>
       </c>
       <c r="C62" s="50" t="n">
         <f aca="false">SUMIFS(MATERIALES!$E$5:$E$14,MATERIALES!$A$5:$A$14,"B.7",MATERIALES!$J$5:$J$14,"P2")</f>
@@ -13356,27 +13690,27 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="27" t="s">
-        <v>641</v>
+        <v>664</v>
       </c>
       <c r="C63" s="50" t="n">
-        <f aca="false">INVERSIONES!$F$9</f>
-        <v>4264.70588235294</v>
+        <f aca="false">INVERSIONES!$F$10</f>
+        <v>4048.03921568627</v>
       </c>
       <c r="D63" s="27"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="27" t="s">
-        <v>642</v>
+        <v>665</v>
       </c>
       <c r="C64" s="50" t="n">
-        <f aca="false">SUMIFS(INVERSIONES!$E$14:$E$23,INVERSIONES!$F$14:$F$23,"P2")</f>
-        <v>42000</v>
+        <f aca="false">SUMIFS(INVERSIONES!$E$15:$E$27,INVERSIONES!$F$15:$F$27,"P2")</f>
+        <v>36000</v>
       </c>
       <c r="D64" s="27"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="26" t="s">
-        <v>643</v>
+        <v>666</v>
       </c>
       <c r="C65" s="41" t="n">
         <f aca="false">($G$51+C55)*tasa_ind</f>
@@ -13386,45 +13720,45 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="32" t="s">
-        <v>644</v>
+        <v>667</v>
       </c>
       <c r="C66" s="43" t="n">
         <f aca="false">SUM(C55:C65)</f>
-        <v>113608.650882353</v>
+        <v>88740.9342156863</v>
       </c>
       <c r="D66" s="31"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="53" t="s">
-        <v>648</v>
+        <v>671</v>
       </c>
       <c r="C67" s="54" t="n">
         <f aca="false">$G$51+$C$66</f>
-        <v>146625.950882353</v>
+        <v>121758.234215686</v>
       </c>
       <c r="D67" s="55"/>
     </row>
     <row r="69" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="56" t="s">
-        <v>649</v>
+        <v>672</v>
       </c>
       <c r="C69" s="57" t="n">
         <f aca="false">PRESUPUESTO!$C$30+PRESUPUESTO!$C$67</f>
-        <v>218910.477</v>
+        <v>185347.583666667</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="15" t="s">
-        <v>650</v>
+        <v>673</v>
       </c>
       <c r="C71" s="58" t="n">
-        <f aca="false">PERSONAL!$H$68+PERSONAL!$H$77+PERSONAL!$K$61+PERSONAL!$K$31+PERSONAL!$H$86+VIAJES!$N$33+SUMIF(MATERIALES!$A$5:$A$14,"B.2",MATERIALES!$E$5:$E$14)+SUMIF(MATERIALES!$A$5:$A$14,"B.3",MATERIALES!$E$5:$E$14)+SUMIF(MATERIALES!$A$5:$A$14,"B.4",MATERIALES!$E$5:$E$14)+SUMIF(MATERIALES!$A$5:$A$14,"B.5",MATERIALES!$E$5:$E$14)+SUMIF(MATERIALES!$A$5:$A$14,"B.6",MATERIALES!$E$5:$E$14)+SUMIF(MATERIALES!$A$5:$A$14,"B.7",MATERIALES!$E$5:$E$14)+INVERSIONES!$G$9+INVERSIONES!$E$24</f>
-        <v>205661.34</v>
+        <f aca="false">PERSONAL!$H$68+PERSONAL!$H$77+PERSONAL!$K$61+PERSONAL!$K$31+PERSONAL!$H$86+VIAJES!$N$33+SUMIF(MATERIALES!$A$5:$A$14,"B.2",MATERIALES!$E$5:$E$14)+SUMIF(MATERIALES!$A$5:$A$14,"B.3",MATERIALES!$E$5:$E$14)+SUMIF(MATERIALES!$A$5:$A$14,"B.4",MATERIALES!$E$5:$E$14)+SUMIF(MATERIALES!$A$5:$A$14,"B.5",MATERIALES!$E$5:$E$14)+SUMIF(MATERIALES!$A$5:$A$14,"B.6",MATERIALES!$E$5:$E$14)+SUMIF(MATERIALES!$A$5:$A$14,"B.7",MATERIALES!$E$5:$E$14)+INVERSIONES!$G$10+INVERSIONES!$E$28</f>
+        <v>172098.446666667</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
-        <v>651</v>
+        <v>674</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -13446,18 +13780,18 @@
       </c>
       <c r="D75" s="12"/>
       <c r="E75" s="12" t="s">
-        <v>554</v>
+        <v>568</v>
       </c>
       <c r="F75" s="12" t="s">
-        <v>652</v>
+        <v>675</v>
       </c>
       <c r="G75" s="12" t="s">
-        <v>653</v>
+        <v>676</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="27" t="s">
-        <v>654</v>
+        <v>677</v>
       </c>
       <c r="C76" s="50" t="n">
         <f aca="false">PERSONAL!$H$86</f>
@@ -13466,11 +13800,11 @@
       <c r="D76" s="27"/>
       <c r="E76" s="50" t="n">
         <f aca="false">PRESUPUESTO!$C$71*tope_coord</f>
-        <v>41132.268</v>
+        <v>34419.6893333333</v>
       </c>
       <c r="F76" s="37" t="n">
         <f aca="false">C76/E76</f>
-        <v>0.644871807214715</v>
+        <v>0.7706356598144</v>
       </c>
       <c r="G76" s="59" t="str">
         <f aca="false">IF(C76&lt;=E76,"OK","SUPERADO")</f>
@@ -13479,20 +13813,20 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="27" t="s">
-        <v>655</v>
+        <v>678</v>
       </c>
       <c r="C77" s="50" t="n">
         <f aca="false">VIAJES!$N$33</f>
-        <v>54683.76</v>
+        <v>27489.2</v>
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="50" t="n">
         <f aca="false">PRESUPUESTO!$C$71*tope_viajes</f>
-        <v>82264.536</v>
+        <v>68839.3786666667</v>
       </c>
       <c r="F77" s="37" t="n">
         <f aca="false">C77/E77</f>
-        <v>0.66473066838911</v>
+        <v>0.399323766896676</v>
       </c>
       <c r="G77" s="59" t="str">
         <f aca="false">IF(C77&lt;=E77,"OK","SUPERADO")</f>
@@ -13501,20 +13835,20 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="27" t="s">
-        <v>656</v>
+        <v>679</v>
       </c>
       <c r="C78" s="50" t="n">
-        <f aca="false">INVERSIONES!$G$9+INVERSIONES!$E$24</f>
-        <v>49250</v>
+        <f aca="false">INVERSIONES!$G$10+INVERSIONES!$E$28</f>
+        <v>42881.6666666667</v>
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="50" t="n">
         <f aca="false">PRESUPUESTO!$C$71*tope_inv</f>
-        <v>102830.67</v>
+        <v>86049.2233333333</v>
       </c>
       <c r="F78" s="37" t="n">
         <f aca="false">C78/E78</f>
-        <v>0.478942712325029</v>
+        <v>0.498338799649054</v>
       </c>
       <c r="G78" s="59" t="str">
         <f aca="false">IF(C78&lt;=E78,"OK","SUPERADO")</f>
@@ -13523,7 +13857,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="27" t="s">
-        <v>657</v>
+        <v>680</v>
       </c>
       <c r="C79" s="50" t="n">
         <f aca="false">SUMIF(MATERIALES!$A$5:$A$14,"B.2",MATERIALES!$E$5:$E$14)</f>
@@ -13545,7 +13879,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="27" t="s">
-        <v>658</v>
+        <v>681</v>
       </c>
       <c r="C80" s="50" t="n">
         <f aca="false">SUMIF(MATERIALES!$A$5:$A$14,"B.4",MATERIALES!$E$5:$E$14)</f>
@@ -13567,7 +13901,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="27" t="s">
-        <v>659</v>
+        <v>682</v>
       </c>
       <c r="C81" s="50" t="n">
         <f aca="false">SUMIF(MATERIALES!$A$5:$A$14,"B.7",MATERIALES!$E$5:$E$14)</f>
@@ -13589,11 +13923,11 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="27" t="s">
-        <v>660</v>
+        <v>683</v>
       </c>
       <c r="C82" s="50" t="n">
         <f aca="false">PRESUPUESTO!$C$69</f>
-        <v>218910.477</v>
+        <v>185347.583666667</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="50" t="n">
@@ -13602,7 +13936,7 @@
       </c>
       <c r="F82" s="37" t="n">
         <f aca="false">C82/E82</f>
-        <v>0.437820954</v>
+        <v>0.370695167333333</v>
       </c>
       <c r="G82" s="59" t="str">
         <f aca="false">IF(C82&lt;=E82,"OK","SUPERADO")</f>
@@ -13611,11 +13945,11 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="27" t="s">
-        <v>661</v>
+        <v>684</v>
       </c>
       <c r="C83" s="50" t="n">
         <f aca="false">PRESUPUESTO!$C$69</f>
-        <v>218910.477</v>
+        <v>185347.583666667</v>
       </c>
       <c r="D83" s="27"/>
       <c r="E83" s="50" t="n">
@@ -13624,7 +13958,7 @@
       </c>
       <c r="F83" s="37" t="n">
         <f aca="false">C83/E83</f>
-        <v>3.12729252857143</v>
+        <v>2.64782262380952</v>
       </c>
       <c r="G83" s="59" t="str">
         <f aca="false">IF(C83&gt;=E83,"OK","BAJO MIN")</f>
